--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Audit Log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cash Flow Reconciliation" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -59,7 +60,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +70,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -109,6 +115,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -495,7 +506,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-10T07:40:40. Source: PSX company payout announcements (board-meeting/announcement date).</t>
+          <t>Last updated 2026-07-10T09:02:42. Source: PSX company payout announcements (board-meeting/announcement date).</t>
         </is>
       </c>
     </row>
@@ -1778,6 +1789,366 @@
           <t>2026-04-30</t>
         </is>
       </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>AICL</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Adamjee Insurance Company Limited</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>PTL</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Panther Tyres Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Automobile Parts &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>BYCO</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Byco Petroleum Pakistan Limited</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Refinery</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>CPPL</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Cherat Packaging Limited</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Paper &amp; Board</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>FDIBL</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>First Dawood Investment Bank Limited</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Investment Banks / Companies</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>SRVI</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Service Industries Limited</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Leather &amp; Tanneries</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>PKGS</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Packages Limited</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Paper &amp; Board</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>AKBL</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Askari Bank Limited</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>MUREB</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Murree Brewery Company Limited</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Food &amp; Personal Care Products</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>GGL</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Ghani Global Holdings Limited</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>TPL</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>TPL Corp Limited</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; Communication</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>BFAGRO</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Barkat Frisian Agro Limited</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Food &amp; Personal Care Products</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>ATLH</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Atlas Honda Limited</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Automobile Assembler</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>PIOC</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Pioneer Cement Limited</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>SRR</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Signature Residency Reit</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Real Estate Investment Trust</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5322,4 +5693,2234 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cash Flow Reconciliation — July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is this period's (current month's) actual per-share cash dividend. Tax withheld at 15%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Dividend Announced (PKR/share)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Gross Cash Dividend (PKR)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Tax Amount (15%) (PKR)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Net Cash Dividend (PKR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MCB</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>MCB Bank Limited</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>362505</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>HBL</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Habib Bank Limited</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>666420</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>BAFL</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Bank Alfalah Limited</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>1311530</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>BAHL</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Bank AL Habib Limited</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>1600298</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>MEBL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Meezan Bank Limited</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>80383</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>HMB</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Habib Metropolitan Bank Limited</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>625687</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>United Bank Limited</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>176300</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>LUCK</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Lucky Cement Limited</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>KOHC</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Kohat Cement Company Limited</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>DGKC</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>D.G. Khan Cement Company Limited</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>201936</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>CHCC</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Cherat Cement Company Limited</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>FCCL</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Fauji Cement Company Limited</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>436625</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>MLCF</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Maple Leaf Cement Factory Limited</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ENGROH</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Engro Holdings Limited</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>EFERT</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Engro Fertilizers Limited</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>FATIMA</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Fatima Fertilizer Company Limited</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>FFC</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Fauji Fertilizer Company Limited</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>583091</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Pakistan Oilfields Limited</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>PSO</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Pakistan State Oil Company Limited</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>MARI</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Mari Energies Limited</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>PPL</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Pakistan Petroleum Limited</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>OGDC</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas Development Company Limited</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>17000</v>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ALTN</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Altern Energy Limited</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>821</v>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NCPL</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Nishat Chunian Power Limited</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>21358</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>KOHE</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Kohinoor Energy Limited</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPL</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Nishat Power Limited</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>30909</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>HUBC</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>The Hub Power Company Limited</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ISL</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>International Steels Limited</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>AGHA</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Agha Steel Industries Limited</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ASTL</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Amreli Steels Limited</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Aisha Steel Mills Limited</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>166000</v>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>CEPB</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Century Paper &amp; Board Mills Limited</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>INDU</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Indus Motor Company Limited</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>NML</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Nishat Mills Limited</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>AGIL</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Agriauto Industries Limited</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>138635</v>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>OLPL</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>OLP Financial Services Pakistan Limited</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>EPCL</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Engro Polymer &amp; Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>ABOT</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Abbott Laboratories (Pakistan) Limited</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>FEROZ</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Ferozsons Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>GLAXO</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>GlaxoSmithKline Pakistan Limited</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>HINOON</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Highnoon Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>7877</v>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>CPHL</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Citi Pharma Limited</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>AGP</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>AGP Limited</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>39088</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SYS</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Systems Limited</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>101000</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>TRG</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>TRG Pakistan Limited</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>AVN</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Avanceon Limited</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>AICL</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Adamjee Insurance Company Limited</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>PTL</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Panther Tyres Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>204610</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>BYCO</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Byco Petroleum Pakistan Limited</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>CPPL</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Cherat Packaging Limited</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>23655</v>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>FDIBL</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>First Dawood Investment Bank Limited</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>SRVI</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Service Industries Limited</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>23062</v>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>PKGS</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Packages Limited</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>AKBL</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Askari Bank Limited</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>449000</v>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>MUREB</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Murree Brewery Company Limited</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>33295</v>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>GGL</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Ghani Global Holdings Limited</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>TPL</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>TPL Corp Limited</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>BFAGRO</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Barkat Frisian Agro Limited</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>17857</v>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>ATLH</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Atlas Honda Limited</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>12125</v>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>PIOC</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Pioneer Cement Limited</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>123472</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>SRR</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Signature Residency Reit</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="n">
+        <v>19829</v>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="n"/>
+      <c r="C66" s="11" t="n">
+        <v>7898068</v>
+      </c>
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-10T09:02:42. Source: PSX company payout announcements (board-meeting/announcement date).</t>
+          <t>Last updated 2026-07-10T09:25:41. Source: PSX company payout announcements (board-meeting/announcement date).</t>
         </is>
       </c>
     </row>
@@ -1810,9 +1810,13 @@
         <v>0</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -1834,9 +1838,13 @@
         <v>0</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -1882,9 +1890,13 @@
         <v>0</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -1930,9 +1942,13 @@
         <v>0</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="5" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -1954,9 +1970,13 @@
         <v>0</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -1978,9 +1998,13 @@
         <v>0</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -2002,9 +2026,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="5" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -2098,9 +2126,13 @@
         <v>0</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -2124,7 +2156,11 @@
       <c r="E64" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -2161,7 +2197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2242,99 +2278,99 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>ATLH</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2026 2:58 PM</t>
+          <t>April 30, 2026 2:52 PM</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>31/03/2026(YR)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>85%(i) (D)</t>
+          <t>560%(F) (D)</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>8.5</v>
+        <v>56</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>8.5</v>
+        <v>56</v>
       </c>
       <c r="G3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2026 3:18 PM</t>
+          <t>April 29, 2026 2:58 PM</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>20%(iii) (D)</t>
+          <t>85%(i) (D)</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="G4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2026 3:56 PM</t>
+          <t>April 29, 2026 3:18 PM</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IIIQ)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>32.50%(iii) (D)</t>
+          <t>20%(iii) (D)</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="G5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2026 4:03 PM</t>
+          <t>April 29, 2026 3:56 PM</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -2344,26 +2380,26 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>15%(i) (D)</t>
+          <t>32.50%(iii) (D)</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="G6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2026 4:02 PM</t>
+          <t>April 28, 2026 4:03 PM</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2387,12 +2423,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>April 27, 2026 3:50 PM</t>
+          <t>April 28, 2026 4:02 PM</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2402,26 +2438,26 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>510%(iii) (D)</t>
+          <t>15%(i) (D)</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>51</v>
+        <v>1.5</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>51</v>
+        <v>1.5</v>
       </c>
       <c r="G8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>OLPL</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>April 27, 2026 3:57 PM</t>
+          <t>April 27, 2026 3:50 PM</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2431,55 +2467,55 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>510%(iii) (D)</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>OLPL</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>April 24, 2026 4:35 PM</t>
+          <t>April 27, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ) - 31/03/2026(IQ)</t>
+          <t>31/03/2026(IIIQ)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>25%(i) (D)  -  25%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>AKBL</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 3:56 PM</t>
+          <t>April 27, 2026 3:54 PM</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2489,55 +2525,55 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>90%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 3:49 PM</t>
+          <t>April 24, 2026 4:35 PM</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>31/03/2026(IQ) - 31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>30%(i) (D)</t>
+          <t>25%(i) (D)  -  25%(i) (D)</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 4:04 PM</t>
+          <t>April 23, 2026 3:56 PM</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2547,26 +2583,26 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>90%(i) (D)</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="G13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 3:51 PM</t>
+          <t>April 23, 2026 3:49 PM</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -2576,200 +2612,200 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>75%(i) (D)</t>
+          <t>30%(i) (D)</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>April 22, 2026 12:35 PM</t>
+          <t>April 23, 2026 4:04 PM</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IIIQ)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>50%(iii) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="G15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>April 20, 2026 3:41 PM</t>
+          <t>April 23, 2026 3:51 PM</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IIIQ)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>75%(i) (D)</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="G16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>April 17, 2026 5:10 PM</t>
+          <t>April 22, 2026 12:35 PM</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>31/03/2026(IIIQ)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>60%(i) (D)</t>
+          <t>50%(iii) (D)</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>April 15, 2026 3:51 PM</t>
+          <t>April 20, 2026 3:41 PM</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>31/03/2026(IIIQ)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>160%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>HINOON</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>April 7, 2026 4:00 PM</t>
+          <t>April 17, 2026 5:10 PM</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>500%(F) (D)</t>
+          <t>60%(i) (D)</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="G19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>SYS</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>April 7, 2026 3:57 PM</t>
+          <t>April 15, 2026 3:51 PM</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>160%(i) (D)</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>HINOON</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>March 26, 2026 3:54 PM</t>
+          <t>April 7, 2026 4:00 PM</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2779,26 +2815,26 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>120%(F) (D)</t>
+          <t>500%(F) (D)</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="G21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>AGP</t>
+          <t>SYS</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>March 24, 2026 4:16 PM</t>
+          <t>April 7, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2808,26 +2844,26 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>60%(F) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>ABOT</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>March 16, 2026 2:30 PM</t>
+          <t>March 26, 2026 3:54 PM</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2837,26 +2873,26 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>400%(F) (D)</t>
+          <t>120%(F) (D)</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>PKGS</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>March 9, 2026 2:14 PM</t>
+          <t>March 26, 2026 3:56 PM</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2866,26 +2902,26 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>160%(F) (D)</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2.5</v>
+        <v>16</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>2.5</v>
+        <v>16</v>
       </c>
       <c r="G24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>AGP</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>February 25, 2026 12:28 PM</t>
+          <t>March 24, 2026 4:16 PM</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2895,142 +2931,142 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>160%(F) (D)</t>
+          <t>60%(F) (D)</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>SRVI</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>February 24, 2026 2:17 PM</t>
+          <t>March 18, 2026 2:33 PM</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>275%(i) (D)</t>
+          <t>175%(F) (D)</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>27.5</v>
+        <v>17.5</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>27.5</v>
+        <v>17.5</v>
       </c>
       <c r="G26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>ABOT</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>February 24, 2026 2:38 PM</t>
+          <t>March 16, 2026 2:30 PM</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>50%(ii) (D)</t>
+          <t>400%(F) (D)</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="G27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>February 23, 2026 1:25 PM</t>
+          <t>March 9, 2026 2:14 PM</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>42.50%(ii) (D)</t>
+          <t>25%(F) (D)</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="G28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>PTL</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>February 23, 2026 1:14 PM</t>
+          <t>March 5, 2026 2:45 PM</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>460%(ii) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="G29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>February 18, 2026 3:51 PM</t>
+          <t>February 25, 2026 12:28 PM</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -3040,26 +3076,26 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>60%(F) (D)</t>
+          <t>160%(F) (D)</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>CHCC</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>February 18, 2026 3:39 PM</t>
+          <t>February 24, 2026 2:17 PM</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3069,84 +3105,84 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>15%(i) (D)</t>
+          <t>275%(i) (D)</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.5</v>
+        <v>27.5</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1.5</v>
+        <v>27.5</v>
       </c>
       <c r="G31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>February 16, 2026 4:25 PM</t>
+          <t>February 24, 2026 2:38 PM</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>30%(F) (D)</t>
+          <t>50%(ii) (D)</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>February 13, 2026 3:57 PM</t>
+          <t>February 23, 2026 1:25 PM</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>45%F) (D)</t>
+          <t>42.50%(ii) (D)</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="G33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>February 13, 2026 4:00 PM</t>
+          <t>February 23, 2026 1:14 PM</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3156,84 +3192,84 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>20%(F) (D)</t>
+          <t>460%(ii) (D)</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="G34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>MUREB</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>February 12, 2026 3:27 PM</t>
+          <t>February 23, 2026 1:19 PM</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>120%(F) (D)</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>CPPL</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>February 11, 2026 3:57 PM</t>
+          <t>February 19, 2026 2:22 PM</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>45%(F) (D)</t>
+          <t>10%(i) (D)</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="G36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>February 9, 2026 3:36 PM</t>
+          <t>February 18, 2026 3:51 PM</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -3243,65 +3279,65 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>70%(F) (D)</t>
+          <t>60%(F) (D)</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>CHCC</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>January 29, 2026 3:14 PM</t>
+          <t>February 18, 2026 3:39 PM</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>85%(F) (D)</t>
+          <t>15%(i) (D)</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="G38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>AICL</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>January 27, 2026 4:55 PM</t>
+          <t>February 18, 2026 4:09 PM</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>20%(F) (D)</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
@@ -3315,58 +3351,58 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>MARI</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>January 26, 2026 4:05 PM</t>
+          <t>February 16, 2026 4:25 PM</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>83%(i) (D)</t>
+          <t>30%(F) (D)</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>3</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>3</v>
       </c>
       <c r="G40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>October 30, 2025 4:28 PM</t>
+          <t>February 13, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IQ)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>50%(i) (D)</t>
+          <t>45%F) (D)</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G41" s="7" t="inlineStr"/>
     </row>
@@ -3378,17 +3414,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>October 29, 2025 3:14 PM</t>
+          <t>February 13, 2026 4:00 PM</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IQ)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>20%(F) (D)</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -3402,58 +3438,58 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>October 29, 2025 4:08 PM</t>
+          <t>February 12, 2026 3:27 PM</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IQ)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>40%(F) (D)</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>October 28, 2025 4:40 PM</t>
+          <t>February 11, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IQ)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>510%(i) (D)</t>
+          <t>45%(F) (D)</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>51</v>
+        <v>4.5</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>51</v>
+        <v>4.5</v>
       </c>
       <c r="G44" s="7" t="inlineStr"/>
     </row>
@@ -3465,17 +3501,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>October 27, 2025 11:09 AM</t>
+          <t>February 9, 2026 3:36 PM</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>70%(iii) (D)</t>
+          <t>70%(F) (D)</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
@@ -3489,650 +3525,650 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>AKBL</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>October 27, 2025 11:03 AM</t>
+          <t>February 9, 2026 3:47 PM</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>25%(iii) (D)</t>
+          <t>17.50% (D)</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:48 PM</t>
+          <t>January 29, 2026 3:14 PM</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>50%(iii) (D)</t>
+          <t>85%(F) (D)</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:27 PM</t>
+          <t>January 27, 2026 4:55 PM</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>30/09/2025(HYR)</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>25%(iii) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>MARI</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:50 PM</t>
+          <t>January 26, 2026 4:05 PM</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>35%(iii) (D)</t>
+          <t>83%(i) (D)</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>3.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:41 PM</t>
+          <t>October 30, 2025 4:28 PM</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>30/09/2025(IQ)</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>95%(iii) (D)</t>
+          <t>50%(i) (D)</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="G50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>ATLH</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>October 22, 2025 3:42 PM</t>
+          <t>October 30, 2025 4:18 PM</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>30/09/2025(HYR)</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>90%(iii) (D)</t>
+          <t>460%(i) (D)</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="G51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>October 15, 2025 3:53 PM</t>
+          <t>October 29, 2025 3:14 PM</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>30/09/2025(IQ)</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>160%(iii) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>October 15, 2025 3:50 PM</t>
+          <t>October 29, 2025 4:08 PM</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>30/09/2025(IQ)</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>45%(iii) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>CPHL</t>
+          <t>AKBL</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>October 2, 2025 4:35 PM</t>
+          <t>October 29, 2025 3:16 PM</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>35%(F) (D)</t>
+          <t>12.5%(ii (D)</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="G54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>NML</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>September 30, 2025 3:34 PM</t>
+          <t>October 28, 2025 4:40 PM</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IQ)</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>20%(F) (D)</t>
+          <t>510%(i) (D)</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>OLPL</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>September 25, 2025 4:24 PM</t>
+          <t>October 27, 2025 11:09 AM</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>35%(F) (D)</t>
+          <t>70%(iii) (D)</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="G56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>September 23, 2025 4:03 PM</t>
+          <t>October 27, 2025 11:03 AM</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>50%(F) (D)</t>
+          <t>25%(iii) (D)</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>FEROZ</t>
+          <t>MUREB</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>September 23, 2025 4:40 PM</t>
+          <t>October 27, 2025 11:15 AM</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IQ)</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>50%(i) (D)</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>September 19, 2025 4:11 PM</t>
+          <t>October 23, 2025 3:48 PM</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>50%(iii) (D)</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>September 3, 2025 3:56 PM</t>
+          <t>October 23, 2025 3:27 PM</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>25%(iii) (D)</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="G60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>August 29, 2025 5:08 PM</t>
+          <t>October 23, 2025 3:50 PM</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>500%(F) (D)</t>
+          <t>35%(iii) (D)</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>50</v>
+        <v>3.5</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>50</v>
+        <v>3.5</v>
       </c>
       <c r="G61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>DGKC</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>August 28, 2025 4:47 PM</t>
+          <t>October 23, 2025 3:41 PM</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>20%(F) (D)</t>
+          <t>95%(iii) (D)</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="G62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>AGIL</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>August 28, 2025 4:44 PM</t>
+          <t>October 22, 2025 3:42 PM</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>35%(F) (D)</t>
+          <t>90%(iii) (D)</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="G63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>August 27, 2025 4:33 PM</t>
+          <t>October 15, 2025 3:53 PM</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>35%(ii) (D)</t>
+          <t>160%(iii) (D)</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3.5</v>
+        <v>16</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>3.5</v>
+        <v>16</v>
       </c>
       <c r="G64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>August 27, 2025 4:34 PM</t>
+          <t>October 15, 2025 3:50 PM</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>45%(iii) (D)</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>AGP</t>
+          <t>CPHL</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>August 27, 2025 3:59 PM</t>
+          <t>October 2, 2025 4:35 PM</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>35%(F) (D)</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>NML</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>August 26, 2025 3:34 PM</t>
+          <t>September 30, 2025 3:34 PM</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>50%(i) (D)</t>
+          <t>20%(F) (D)</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>CHCC</t>
+          <t>PTL</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>August 21, 2025 3:53 PM</t>
+          <t>September 29, 2025 10:51 AM</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -4142,26 +4178,26 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>DIVIDEND =20%(F)</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>PIOC</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>August 20, 2025 3:40 PM</t>
+          <t>September 29, 2025 10:44 AM</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -4171,26 +4207,26 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>50%(F) (D)</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>PSO</t>
+          <t>OLPL</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>August 19, 2025 4:17 PM</t>
+          <t>September 25, 2025 4:24 PM</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -4200,84 +4236,84 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>35%(F) (D)</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="G70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>August 13, 2025 3:40 PM</t>
+          <t>September 23, 2025 4:03 PM</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>70%(ii) (D)</t>
+          <t>50%(F) (D)</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>FEROZ</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>August 13, 2025 3:38 PM</t>
+          <t>September 23, 2025 4:40 PM</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>25%(ii) (D)</t>
+          <t>40%(F) (D)</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="G72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>LUCK</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 11:11 AM</t>
+          <t>September 19, 2025 4:11 PM</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -4287,26 +4323,26 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>200%(F) (D)</t>
+          <t>25%(F) (D)</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>FCCL</t>
+          <t>MUREB</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 11:05 AM</t>
+          <t>September 19, 2025 4:24 PM</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -4316,26 +4352,26 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>12.50%(F) (D)</t>
+          <t>145%(F) (D)</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1.25</v>
+        <v>14.5</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>1.25</v>
+        <v>14.5</v>
       </c>
       <c r="G74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 3:29 PM</t>
+          <t>September 3, 2025 3:56 PM</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -4345,26 +4381,26 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>500%(F) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>MARI</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 10:57 AM</t>
+          <t>August 29, 2025 5:08 PM</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -4374,84 +4410,84 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>217%(F) (D)</t>
+          <t>500%(F) (D)</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>21.7</v>
+        <v>50</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>21.7</v>
+        <v>50</v>
       </c>
       <c r="G76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>DGKC</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>August 6, 2025 3:49 PM</t>
+          <t>August 28, 2025 4:47 PM</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>90%(ii) (D)</t>
+          <t>20%(F) (D)</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>AGIL</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>July 31, 2025 3:49 PM</t>
+          <t>August 28, 2025 4:44 PM</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>45%(ii) (D)</t>
+          <t>35%(F) (D)</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>AICL</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>July 31, 2025 3:53 PM</t>
+          <t>August 28, 2025 4:17 PM</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -4461,26 +4497,26 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>25%(ii) (D)</t>
+          <t>20%(I) (D)</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>July 30, 2025 3:24 PM</t>
+          <t>August 27, 2025 4:33 PM</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -4490,26 +4526,26 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>42.50%(ii) (D)</t>
+          <t>35%(ii) (D)</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="G80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>July 29, 2025 3:26 PM</t>
+          <t>August 27, 2025 4:34 PM</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -4519,26 +4555,26 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>120%(ii) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="G81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>AGP</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>July 11, 2025 5:05 PM</t>
+          <t>August 27, 2025 3:59 PM</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -4548,565 +4584,565 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>160%(II) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>April 30, 2025 4:16 PM</t>
+          <t>August 26, 2025 3:34 PM</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>30%(iii) (D)</t>
+          <t>50%(i) (D)</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>CHCC</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2025 2:46 PM</t>
+          <t>August 21, 2025 3:53 PM</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>10%(iii) (D)</t>
+          <t>40%(F) (D)</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>AKBL</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2025 3:39 PM</t>
+          <t>August 21, 2025 4:27 PM</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>70%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2025 12:00 PM</t>
+          <t>August 20, 2025 3:40 PM</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>500%(iii) (D)</t>
+          <t>25%(F) (D)</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>50</v>
+        <v>2.5</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>50</v>
+        <v>2.5</v>
       </c>
       <c r="G86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>CPPL</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>April 25, 2025 4:31 PM</t>
+          <t>August 20, 2025 4:14 PM</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>45%(i) (D)</t>
+          <t>20%(F) (D)</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>PSO</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>April 25, 2025 5:30 PM</t>
+          <t>August 19, 2025 4:17 PM</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>20%(iii) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>April 25, 2025 5:26 PM</t>
+          <t>August 13, 2025 3:40 PM</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>20%(iii) (D)</t>
+          <t>70%(ii) (D)</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>April 24, 2025 4:02 PM</t>
+          <t>August 13, 2025 3:38 PM</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>25%(ii) (D)</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>OLPL</t>
+          <t>LUCK</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>April 24, 2025 12:45 PM</t>
+          <t>August 11, 2025 11:11 AM</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>200%(F) (D)</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>FCCL</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2025 3:39 PM</t>
+          <t>August 11, 2025 11:05 AM</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>90%(i) (D)</t>
+          <t>12.50%(F) (D)</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>9</v>
+        <v>1.25</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>9</v>
+        <v>1.25</v>
       </c>
       <c r="G92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2025 3:22 PM</t>
+          <t>August 11, 2025 3:29 PM</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>25%(i) (D)</t>
+          <t>500%(F) (D)</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>2.5</v>
+        <v>50</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>2.5</v>
+        <v>50</v>
       </c>
       <c r="G93" s="7" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>MARI</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>April 22, 2025 5:01 PM</t>
+          <t>August 11, 2025 10:57 AM</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>22.5%(i) (D)</t>
+          <t>217%(F) (D)</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2.25</v>
+        <v>21.7</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>2.25</v>
+        <v>21.7</v>
       </c>
       <c r="G94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>April 21, 2025 4:10 PM</t>
+          <t>August 6, 2025 3:49 PM</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>70%(i) (D)</t>
+          <t>90%(ii) (D)</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G95" s="7" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>April 17, 2025 3:56 PM</t>
+          <t>July 31, 2025 3:49 PM</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>25%(i) (D)</t>
+          <t>45%(ii) (D)</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="G96" s="7" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>April 16, 2025 4:52 PM</t>
+          <t>July 31, 2025 3:53 PM</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>110%(i) (D)</t>
+          <t>25%(ii) (D)</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="G97" s="7" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>HINOON</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>March 26, 2025 2:45 PM</t>
+          <t>July 30, 2025 3:24 PM</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>400%(F) (D)</t>
+          <t>42.50%(ii) (D)</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>40</v>
+        <v>4.25</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>40</v>
+        <v>4.25</v>
       </c>
       <c r="G98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>March 24, 2025 2:13 PM</t>
+          <t>July 29, 2025 3:26 PM</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>120%(ii) (D)</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G99" s="7" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>SYS</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>March 24, 2025 2:14 PM</t>
+          <t>July 11, 2025 5:05 PM</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>60%(F) (D)</t>
+          <t>160%(II) (D)</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>March 14, 2025 1:12 PM</t>
+          <t>April 30, 2025 4:16 PM</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>42.5%(F) (D)</t>
+          <t>30%(iii) (D)</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="G101" s="7" t="inlineStr"/>
     </row>
@@ -5118,53 +5154,53 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 4:26 PM</t>
+          <t>April 29, 2025 2:46 PM</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>20%(ii) (D)</t>
+          <t>10%(iii) (D)</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 4:32 PM</t>
+          <t>April 28, 2025 3:39 PM</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>40.50% (D)</t>
+          <t>70%(i) (D)</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G103" s="7" t="inlineStr"/>
     </row>
@@ -5176,75 +5212,75 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 10:58 AM</t>
+          <t>April 28, 2025 12:00 PM</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>370%(ii) (D)</t>
+          <t>500%(iii) (D)</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>AGP</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 11:04 AM</t>
+          <t>April 25, 2025 4:31 PM</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>45%(i) (D)</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>February 27, 2025 2:56 PM</t>
+          <t>April 25, 2025 5:30 PM</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>20%(iii) (D)</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -5258,203 +5294,203 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>February 26, 2025 12:53 PM</t>
+          <t>April 25, 2025 5:26 PM</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>50%(i) (D)</t>
+          <t>20%(iii) (D)</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>CHCC</t>
+          <t>MUREB</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>February 21, 2025 2:43 PM</t>
+          <t>April 25, 2025 3:07 PM</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>15%(i) (D)</t>
+          <t>100%(iii) (D)</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="G108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>ALTN</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>February 21, 2025 5:00 PM</t>
+          <t>April 24, 2025 4:02 PM</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>97%(i) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="G109" s="7" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>OLPL</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>February 20, 2025 3:24 PM</t>
+          <t>April 24, 2025 12:45 PM</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>45%(F) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G110" s="7" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>ABOT</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>February 20, 2025 3:45 PM</t>
+          <t>April 23, 2025 3:39 PM</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>90%(i) (D)</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>February 19, 2025 3:45 PM</t>
+          <t>April 23, 2025 3:22 PM</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>42.5%(F) (D)</t>
+          <t>25%(i) (D)</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="G112" s="7" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>February 19, 2025 3:42 PM</t>
+          <t>April 22, 2025 5:01 PM</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>110%(F) (D)</t>
+          <t>22.5%(i) (D)</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>11</v>
+        <v>2.25</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>11</v>
+        <v>2.25</v>
       </c>
       <c r="G113" s="7" t="inlineStr"/>
     </row>
@@ -5466,17 +5502,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>February 13, 2025 3:30 PM</t>
+          <t>April 21, 2025 4:10 PM</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>70%(F) (D)</t>
+          <t>70%(i) (D)</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -5490,70 +5526,70 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>February 10, 2025 3:39 PM</t>
+          <t>April 17, 2025 3:56 PM</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>80%(F) (D)</t>
+          <t>25%(i) (D)</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>February 6, 2025 4:25 PM</t>
+          <t>April 16, 2025 4:52 PM</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>90%(F) (D)</t>
+          <t>110%(i) (D)</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>HINOON</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>January 30, 2025 4:00 PM</t>
+          <t>March 26, 2025 2:45 PM</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
@@ -5563,26 +5599,26 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>400%(F) (D)</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2.5</v>
+        <v>40</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>2.5</v>
+        <v>40</v>
       </c>
       <c r="G117" s="7" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>SRVI</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>January 30, 2025 4:05 PM</t>
+          <t>March 26, 2025 2:23 PM</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -5592,26 +5628,26 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>65%(F) (D)</t>
+          <t>150%(F) (D)</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>6.5</v>
+        <v>15</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>6.5</v>
+        <v>15</v>
       </c>
       <c r="G118" s="7" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>PKGS</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>January 29, 2025 3:36 PM</t>
+          <t>March 26, 2025 2:30 PM</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
@@ -5621,74 +5657,828 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>210%(F) (D)</t>
+          <t>150%(F) (D)</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G119" s="7" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>January 27, 2025 4:28 PM</t>
+          <t>March 24, 2025 2:13 PM</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/12/2024(YR)</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>250%(i) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G120" s="7" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
+          <t>SYS</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>March 24, 2025 2:14 PM</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>60%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>FATIMA</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>March 14, 2025 1:12 PM</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>42.5%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>AICL</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>March 4, 2025 2:31 PM</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>15%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>PPL</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>February 28, 2025 4:26 PM</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(HYR)</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>20%(ii) (D)</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>OGDC</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>February 28, 2025 4:32 PM</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(HYR)</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>40.50% (D)</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>INDU</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>February 28, 2025 10:58 AM</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(HYR)</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>370%(ii) (D)</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>AGP</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>February 28, 2025 11:04 AM</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>40%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>PIOC</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>February 28, 2025 4:24 PM</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>50%(i) (D)</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>NPL</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>February 27, 2025 2:56 PM</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(HYR)</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>20%(i) (D)</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>HUBC</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>February 26, 2025 12:53 PM</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(HYR)</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>50%(i) (D)</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>AKBL</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>February 24, 2025 4:18 PM</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>30%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>CHCC</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>February 21, 2025 2:43 PM</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(HYR)</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>15%(i) (D)</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>ALTN</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>February 21, 2025 5:00 PM</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>97%(i) (D)</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G133" s="7" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>MUREB</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>February 21, 2025 2:40 PM</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(HYR)</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>120%(ii) (D)</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>HMB</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>February 20, 2025 3:24 PM</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>45%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>ABOT</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>February 20, 2025 3:45 PM</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>100%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>CPPL</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>February 20, 2025 3:39 PM</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(HYR)</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>10%(i) (D)</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="7" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>HBL</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>February 19, 2025 3:45 PM</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>42.5%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>February 19, 2025 3:42 PM</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>110%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>MEBL</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>February 13, 2025 3:30 PM</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>70%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>EFERT</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>February 10, 2025 3:39 PM</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>80%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>MCB</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>February 6, 2025 4:25 PM</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>90%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>BAFL</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>January 30, 2025 4:00 PM</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>25%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>BAHL</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>January 30, 2025 4:05 PM</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>65%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>FFC</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>January 29, 2025 3:36 PM</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>210%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>January 27, 2025 4:28 PM</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(HYR)</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>250%(i) (D)</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
           <t>NCPL</t>
         </is>
       </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B147" s="5" t="inlineStr">
         <is>
           <t>November 13, 2024 4:33 PM</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>50%(I) (D)</t>
         </is>
       </c>
-      <c r="E121" s="5" t="n">
+      <c r="E147" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F121" s="5" t="n">
+      <c r="F147" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G121" s="7" t="inlineStr"/>
+      <c r="G147" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-10T09:25:41. Source: PSX company payout announcements (board-meeting/announcement date).</t>
+          <t>Last updated 2026-07-10T09:31:36. Source: PSX company payout announcements (board-meeting/announcement date).</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is this period's (current month's) actual per-share cash dividend. Tax withheld at 15%.</t>
+          <t>Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is the actual per-share cash dividend from the announcement(s) that triggered this update. Tax withheld at 15%.</t>
         </is>
       </c>
     </row>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-10T10:06:58. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is the actual per-share cash dividend from the announcement(s) that triggered this update. Tax withheld at 15%.</t>
+          <t>Last updated 2026-07-10T10:09:49. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is the actual per-share cash dividend from the announcement(s) that triggered this update. Tax withheld at 15%.</t>
         </is>
       </c>
     </row>
@@ -601,25 +601,17 @@
       <c r="F5" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G5" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>3262545</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>489381.75</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>2773163.25</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
@@ -657,25 +649,17 @@
       <c r="F6" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G6" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>7997040</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1199556</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>6797484</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
@@ -713,25 +697,17 @@
       <c r="F7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>7869180</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1180377</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>6688803</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -769,25 +745,17 @@
       <c r="F8" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G8" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>12802384</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1920357.6</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>10882026.4</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
@@ -825,25 +793,17 @@
       <c r="F9" s="7" t="n">
         <v>14.5</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G9" s="7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1165553.5</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>174833.025</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>990720.475</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -881,25 +841,17 @@
       <c r="F10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>3128435</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>469265.25</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>2659169.75</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
@@ -937,25 +889,17 @@
       <c r="F11" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G11" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>5641600</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>846240</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>4795360</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
@@ -1153,25 +1097,17 @@
       <c r="F15" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G15" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
@@ -1361,25 +1297,17 @@
       <c r="F19" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G19" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
@@ -1417,25 +1345,17 @@
       <c r="F20" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -1473,25 +1393,17 @@
       <c r="F21" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>9912547</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>1486882.05</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>8425664.949999999</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
@@ -1529,25 +1441,17 @@
       <c r="F22" s="7" t="n">
         <v>27.5</v>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G22" s="7" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
@@ -1641,25 +1545,17 @@
       <c r="F24" s="7" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G24" s="7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
@@ -1697,25 +1593,17 @@
       <c r="F25" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G25" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>80000</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>68000</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
@@ -1753,25 +1641,17 @@
       <c r="F26" s="7" t="n">
         <v>7.5</v>
       </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G26" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>127500</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>19125</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>108375</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
@@ -1865,25 +1745,17 @@
       <c r="F28" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G28" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>32037</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>4805.55</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>27231.45</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -1969,25 +1841,17 @@
       <c r="F30" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G30" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>46363.5</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>6954.525</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>39408.975</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
@@ -2025,25 +1889,17 @@
       <c r="F31" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G31" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
@@ -2081,25 +1937,17 @@
       <c r="F32" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
@@ -2329,25 +2177,17 @@
       <c r="F37" s="7" t="n">
         <v>97</v>
       </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G37" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
@@ -2497,25 +2337,17 @@
       <c r="F40" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -2601,25 +2433,17 @@
       <c r="F42" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G42" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
@@ -2713,25 +2537,17 @@
       <c r="F44" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G44" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
@@ -2769,25 +2585,17 @@
       <c r="F45" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G45" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>393850</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>59077.5</v>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>334772.5</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
@@ -2881,25 +2689,17 @@
       <c r="F47" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G47" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>234528</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>35179.2</v>
+      </c>
+      <c r="J47" s="7" t="n">
+        <v>199348.8</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
@@ -2937,25 +2737,17 @@
       <c r="F48" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G48" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>151500</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>858500</v>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
@@ -3041,25 +2833,17 @@
       <c r="F50" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -3097,25 +2881,17 @@
       <c r="F51" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G51" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>8500</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -3153,25 +2929,17 @@
       <c r="F52" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>409220</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>61383</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>347837</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
@@ -3257,25 +3025,17 @@
       <c r="F54" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>23655</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>3548.25</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>20106.75</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
@@ -3361,25 +3121,17 @@
       <c r="F56" s="7" t="n">
         <v>17.5</v>
       </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G56" s="7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>403585</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>60537.75</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>343047.25</v>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
@@ -3417,25 +3169,17 @@
       <c r="F57" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G57" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>240</v>
+      </c>
+      <c r="J57" s="7" t="n">
+        <v>1360</v>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
@@ -3473,25 +3217,17 @@
       <c r="F58" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G58" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>898000</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>134700</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>763300</v>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
@@ -3529,25 +3265,17 @@
       <c r="F59" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G59" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>399540</v>
+      </c>
+      <c r="I59" s="7" t="n">
+        <v>59931</v>
+      </c>
+      <c r="J59" s="7" t="n">
+        <v>339609</v>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
@@ -3729,25 +3457,17 @@
       <c r="F63" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G63" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="H63" s="7" t="n">
+        <v>679000</v>
+      </c>
+      <c r="I63" s="7" t="n">
+        <v>101850</v>
+      </c>
+      <c r="J63" s="7" t="n">
+        <v>577150</v>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
@@ -3879,13 +3599,13 @@
       <c r="F66" s="10" t="n"/>
       <c r="G66" s="10" t="n"/>
       <c r="H66" s="12" t="n">
-        <v>0</v>
+        <v>56528163</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>0</v>
+        <v>8479224.449999999</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>0</v>
+        <v>48048938.55</v>
       </c>
       <c r="K66" s="10" t="n"/>
       <c r="L66" s="10" t="n"/>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-10T10:09:49. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is the actual per-share cash dividend from the announcement(s) that triggered this update. Tax withheld at 15%.</t>
+          <t>Last updated 2026-07-10T10:44:17. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is the actual per-share cash dividend from the announcement(s) that triggered this update. Tax withheld at 15%.</t>
         </is>
       </c>
     </row>
@@ -601,17 +601,25 @@
       <c r="F5" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>3262545</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>489381.75</v>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>2773163.25</v>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
@@ -649,17 +657,25 @@
       <c r="F6" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>7997040</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>1199556</v>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>6797484</v>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
@@ -697,17 +713,25 @@
       <c r="F7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>7869180</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>1180377</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>6688803</v>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -745,17 +769,25 @@
       <c r="F8" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>12802384</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>1920357.6</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>10882026.4</v>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
@@ -793,17 +825,25 @@
       <c r="F9" s="7" t="n">
         <v>14.5</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>1165553.5</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>174833.025</v>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>990720.475</v>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -841,17 +881,25 @@
       <c r="F10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>3128435</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>469265.25</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>2659169.75</v>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
@@ -889,17 +937,25 @@
       <c r="F11" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>5641600</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>846240</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>4795360</v>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
@@ -971,12 +1027,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>KOHC</t>
+          <t>DGKC</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Kohat Cement Company Limited</t>
+          <t>D.G. Khan Cement Company Limited</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -985,7 +1041,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0</v>
+        <v>201936</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
@@ -1013,18 +1069,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
-      <c r="L13" s="8" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>2025-08-28: Rs 2.0</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>DGKC</t>
+          <t>FCCL</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>D.G. Khan Cement Company Limited</t>
+          <t>Fauji Cement Company Limited</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1033,7 +1097,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>201936</v>
+        <v>436625</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1063,24 +1127,24 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>2025-08-28: Rs 2.0</t>
+          <t>2025-08-11: Rs 1.25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>CHCC</t>
+          <t>MLCF</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Cherat Cement Company Limited</t>
+          <t>Maple Leaf Cement Factory Limited</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1089,61 +1153,61 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-18: Rs 1.5; 2025-08-21: Rs 4.0; 2025-02-21: Rs 1.5</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>FCCL</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Fauji Cement Company Limited</t>
+          <t>Fauji Fertilizer Company Limited</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Fertilizers</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>436625</v>
+        <v>583091</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
@@ -1167,39 +1231,39 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>2025-08-11: Rs 1.25</t>
+          <t>2026-04-29: Rs 8.5; 2026-01-29: Rs 8.5; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>MLCF</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Maple Leaf Cement Factory Limited</t>
+          <t>Pakistan Petroleum Limited</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Oil/Gas</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>110000</v>
+        <v>20000</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
@@ -1221,33 +1285,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
-      <c r="L17" s="8" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29: Rs 2.0; 2026-02-13: Rs 2.0; 2025-10-29: Rs 2.0; 2025-09-19: Rs 2.5; 2025-04-29: Rs 1.0; 2025-02-28: Rs 2.0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>ENGROH</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Engro Holdings Limited</t>
+          <t>Oil &amp; Gas Development Company Limited</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Fertilizers</t>
+          <t>Oil/Gas</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
@@ -1269,219 +1341,251 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="8" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29: Rs 3.25; 2026-02-23: Rs 4.25; 2025-10-29: Rs 3.5; 2025-09-23: Rs 5.0; 2025-04-30: Rs 3.0; 2025-02-28: Rs 0.0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>ALTN</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Engro Fertilizers Limited</t>
+          <t>Altern Energy Limited</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Fertilizers</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>2026-04-20: Rs 2.0; 2026-02-12: Rs 4.0; 2025-10-15: Rs 4.5; 2025-07-30: Rs 4.25; 2025-04-22: Rs 2.25; 2025-02-10: Rs 8.0</t>
+          <t>2025-02-21: Rs 9.7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Fatima Fertilizer Company Limited</t>
+          <t>Nishat Chunian Power Limited</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Fertilizers</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0</v>
+        <v>21358</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>0</v>
+        <v>1.5</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>2026-03-09: Rs 2.5; 2025-08-27: Rs 3.5; 2025-03-14: Rs 4.25</t>
+          <t>2026-04-28: Rs 1.5; 2025-04-25: Rs 2.0; 2024-11-13: Rs 5.0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Fauji Fertilizer Company Limited</t>
+          <t>Nishat Power Limited</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Fertilizers</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>583091</v>
+        <v>30909</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>9912547</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>1486882.05</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>8425664.949999999</v>
+        <v>1.5</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29: Rs 8.5; 2026-01-29: Rs 8.5; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
+          <t>2026-04-28: Rs 1.5; 2025-04-25: Rs 2.0; 2025-02-27: Rs 2.0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>ASL</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Pakistan Oilfields Limited</t>
+          <t>Aisha Steel Mills Limited</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Oil/Gas</t>
+          <t>Steel Sector</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0</v>
+        <v>166000</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-24: Rs 27.5; 2025-08-11: Rs 50.0; 2025-01-27: Rs 25.0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>PSO</t>
+          <t>AGIL</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Pakistan State Oil Company Limited</t>
+          <t>Agriauto Industries Limited</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Oil/Gas</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0</v>
+        <v>138635</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>0</v>
@@ -1511,183 +1615,207 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>2025-08-19: Rs 10.0</t>
+          <t>2025-08-28: Rs 3.5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>MARI</t>
+          <t>HINOON</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Mari Energies Limited</t>
+          <t>Highnoon Laboratories Limited</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Oil/Gas</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
+        <v>7877</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>2026-01-26: Rs 8.3; 2025-08-11: Rs 21.7</t>
+          <t>2026-04-07: Rs 50.0; 2025-03-26: Rs 40.0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>AGP</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Pakistan Petroleum Limited</t>
+          <t>AGP Limited</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Oil/Gas</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>20000</v>
+        <v>39088</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>80000</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J25" s="7" t="n">
-        <v>68000</v>
+        <v>6</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29: Rs 2.0; 2026-02-13: Rs 2.0; 2025-10-29: Rs 2.0; 2025-09-19: Rs 2.5; 2025-04-29: Rs 1.0; 2025-02-28: Rs 2.0</t>
+          <t>2026-03-24: Rs 6.0; 2025-08-27: Rs 2.0; 2025-02-28: Rs 4.0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>SYS</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Development Company Limited</t>
+          <t>Systems Limited</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Oil/Gas</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>17000</v>
+        <v>101000</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H26" s="7" t="n">
-        <v>127500</v>
-      </c>
-      <c r="I26" s="7" t="n">
-        <v>19125</v>
-      </c>
-      <c r="J26" s="7" t="n">
-        <v>108375</v>
+        <v>10</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29: Rs 3.25; 2026-02-23: Rs 4.25; 2025-10-29: Rs 3.5; 2025-09-23: Rs 5.0; 2025-04-30: Rs 3.0; 2025-02-28: Rs 0.0</t>
+          <t>2026-04-07: Rs 10.0; 2025-03-24: Rs 6.0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>ALTN</t>
+          <t>AICL</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Altern Energy Limited</t>
+          <t>Adamjee Insurance Company Limited</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>821</v>
+        <v>5000</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
@@ -1711,81 +1839,89 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>2025-02-21: Rs 9.7</t>
+          <t>2026-02-18: Rs 2.0; 2025-08-28: Rs 2.0; 2025-03-04: Rs 1.5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>PTL</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Nishat Chunian Power Limited</t>
+          <t>Panther Tyres Ltd.</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Automobile Parts &amp; Accessories</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>21358</v>
+        <v>204610</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <v>32037</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>4805.55</v>
-      </c>
-      <c r="J28" s="7" t="n">
-        <v>27231.45</v>
+        <v>2</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>2026-04-28: Rs 1.5; 2025-04-25: Rs 2.0; 2024-11-13: Rs 5.0</t>
+          <t>2026-03-05: Rs 2.0; 2025-09-29: Rs 0.0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>KOHE</t>
+          <t>BYCO</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Kohinoor Energy Limited</t>
+          <t>Byco Petroleum Pakistan Limited</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Refinery</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -1819,171 +1955,187 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>CPPL</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Nishat Power Limited</t>
+          <t>Cherat Packaging Limited</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Paper &amp; Board</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>30909</v>
+        <v>23655</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>46363.5</v>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>6954.525</v>
-      </c>
-      <c r="J30" s="7" t="n">
-        <v>39408.975</v>
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>2026-04-28: Rs 1.5; 2025-04-25: Rs 2.0; 2025-02-27: Rs 2.0</t>
+          <t>2026-02-19: Rs 1.0; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>FDIBL</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>The Hub Power Company Limited</t>
+          <t>First Dawood Investment Bank Limited</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Investment Banks / Companies</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-22: Rs 5.0; 2026-02-24: Rs 5.0; 2025-10-30: Rs 5.0; 2025-09-03: Rs 10.0; 2025-02-26: Rs 5.0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>SRVI</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>International Steels Limited</t>
+          <t>Service Industries Limited</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Steel Sector</t>
+          <t>Leather &amp; Tanneries</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0</v>
+        <v>23062</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="7" t="n">
-        <v>0</v>
+        <v>17.5</v>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>2026-01-27: Rs 2.0; 2025-08-20: Rs 2.5</t>
+          <t>2026-03-18: Rs 17.5; 2025-03-26: Rs 15.0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>AGHA</t>
+          <t>PKGS</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Agha Steel Industries Limited</t>
+          <t>Packages Limited</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Steel Sector</t>
+          <t>Paper &amp; Board</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
@@ -2005,33 +2157,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="8" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-26: Rs 16.0; 2025-03-26: Rs 15.0</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>ASTL</t>
+          <t>AKBL</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Amreli Steels Limited</t>
+          <t>Askari Bank Limited</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Steel Sector</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>0</v>
+        <v>449000</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -2053,33 +2213,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="8" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-27: Rs 2.0; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>ASL</t>
+          <t>MUREB</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Aisha Steel Mills Limited</t>
+          <t>Murree Brewery Company Limited</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Steel Sector</t>
+          <t>Food &amp; Personal Care Products</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>166000</v>
+        <v>33295</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
@@ -2101,27 +2269,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="8" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-23: Rs 12.0; 2025-10-27: Rs 5.0; 2025-09-19: Rs 14.5; 2025-04-25: Rs 10.0; 2025-02-21: Rs 12.0</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>CEPB</t>
+          <t>GGL</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Century Paper &amp; Board Mills Limited</t>
+          <t>Ghani Global Holdings Limited</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>0</v>
@@ -2155,69 +2331,69 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Indus Motor Company Limited</t>
+          <t>TPL Corp Limited</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Technology &amp; Communication</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="H37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-27: Rs 51.0; 2026-02-23: Rs 46.0; 2025-10-28: Rs 51.0; 2025-08-29: Rs 50.0; 2025-04-28: Rs 50.0; 2025-02-28: Rs 37.0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>NML</t>
+          <t>BFAGRO</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Nishat Mills Limited</t>
+          <t>Barkat Frisian Agro Limited</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Food &amp; Personal Care Products</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>0</v>
+        <v>17857</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>0</v>
@@ -2245,41 +2421,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t>2025-09-30: Rs 2.0</t>
-        </is>
-      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>AGIL</t>
+          <t>ATLH</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Agriauto Industries Limited</t>
+          <t>Atlas Honda Limited</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Automobile Assembler</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>138635</v>
+        <v>12125</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
@@ -2303,81 +2471,89 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>2025-08-28: Rs 3.5</t>
+          <t>2026-04-30: Rs 56.0; 2025-10-30: Rs 46.0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>OLPL</t>
+          <t>PIOC</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>OLP Financial Services Pakistan Limited</t>
+          <t>Pioneer Cement Limited</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0</v>
+        <v>123472</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="7" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>2026-04-27: Rs 2.0; 2025-09-25: Rs 3.5; 2025-04-24: Rs 2.0</t>
+          <t>2025-09-29: Rs 5.0; 2025-02-28: Rs 5.0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>EPCL</t>
+          <t>SRR</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Engro Polymer &amp; Chemicals Limited</t>
+          <t>Signature Residency Reit</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Real Estate Investment Trust</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0</v>
+        <v>19829</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>0</v>
@@ -2409,1206 +2585,30 @@
       <c r="L41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>ABOT</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Abbott Laboratories (Pakistan) Limited</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-16: Rs 40.0; 2025-02-20: Rs 10.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>FEROZ</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Ferozsons Laboratories Limited</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t>2025-09-23: Rs 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>GLAXO</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>GlaxoSmithKline Pakistan Limited</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-26: Rs 12.0; 2025-08-26: Rs 5.0; 2025-03-24: Rs 10.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>HINOON</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Highnoon Laboratories Limited</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>7877</v>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="H45" s="7" t="n">
-        <v>393850</v>
-      </c>
-      <c r="I45" s="7" t="n">
-        <v>59077.5</v>
-      </c>
-      <c r="J45" s="7" t="n">
-        <v>334772.5</v>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="L45" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-07: Rs 50.0; 2025-03-26: Rs 40.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>CPHL</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Citi Pharma Limited</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t>2025-10-02: Rs 3.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>AGP</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>AGP Limited</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>39088</v>
-      </c>
-      <c r="E47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G47" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H47" s="7" t="n">
-        <v>234528</v>
-      </c>
-      <c r="I47" s="7" t="n">
-        <v>35179.2</v>
-      </c>
-      <c r="J47" s="7" t="n">
-        <v>199348.8</v>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-24: Rs 6.0; 2025-08-27: Rs 2.0; 2025-02-28: Rs 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>SYS</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Systems Limited</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Tech</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="n">
-        <v>101000</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H48" s="7" t="n">
-        <v>1010000</v>
-      </c>
-      <c r="I48" s="7" t="n">
-        <v>151500</v>
-      </c>
-      <c r="J48" s="7" t="n">
-        <v>858500</v>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="L48" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-07: Rs 10.0; 2025-03-24: Rs 6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>TRG</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>TRG Pakistan Limited</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Tech</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="8" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>AVN</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Avanceon Limited</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Tech</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-30: Rs 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>AICL</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Adamjee Insurance Company Limited</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" s="7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I51" s="7" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J51" s="7" t="n">
-        <v>8500</v>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="L51" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-18: Rs 2.0; 2025-08-28: Rs 2.0; 2025-03-04: Rs 1.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>PTL</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>Panther Tyres Ltd.</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Automobile Parts &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="n">
-        <v>204610</v>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" s="7" t="n">
-        <v>409220</v>
-      </c>
-      <c r="I52" s="7" t="n">
-        <v>61383</v>
-      </c>
-      <c r="J52" s="7" t="n">
-        <v>347837</v>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="L52" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-05: Rs 2.0; 2025-09-29: Rs 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>BYCO</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Byco Petroleum Pakistan Limited</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Refinery</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="8" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>CPPL</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>Cherat Packaging Limited</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Paper &amp; Board</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="n">
-        <v>23655</v>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" s="7" t="n">
-        <v>23655</v>
-      </c>
-      <c r="I54" s="7" t="n">
-        <v>3548.25</v>
-      </c>
-      <c r="J54" s="7" t="n">
-        <v>20106.75</v>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="L54" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-19: Rs 1.0; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>FDIBL</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>First Dawood Investment Bank Limited</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>Investment Banks / Companies</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="E55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="8" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>SRVI</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Service Industries Limited</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Leather &amp; Tanneries</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="n">
-        <v>23062</v>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H56" s="7" t="n">
-        <v>403585</v>
-      </c>
-      <c r="I56" s="7" t="n">
-        <v>60537.75</v>
-      </c>
-      <c r="J56" s="7" t="n">
-        <v>343047.25</v>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="L56" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-18: Rs 17.5; 2025-03-26: Rs 15.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>PKGS</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Packages Limited</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Paper &amp; Board</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="G57" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="H57" s="7" t="n">
-        <v>1600</v>
-      </c>
-      <c r="I57" s="7" t="n">
-        <v>240</v>
-      </c>
-      <c r="J57" s="7" t="n">
-        <v>1360</v>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="L57" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-26: Rs 16.0; 2025-03-26: Rs 15.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>AKBL</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>Askari Bank Limited</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="n">
-        <v>449000</v>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" s="7" t="n">
-        <v>898000</v>
-      </c>
-      <c r="I58" s="7" t="n">
-        <v>134700</v>
-      </c>
-      <c r="J58" s="7" t="n">
-        <v>763300</v>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="L58" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-27: Rs 2.0; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>MUREB</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Murree Brewery Company Limited</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Food &amp; Personal Care Products</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>33295</v>
-      </c>
-      <c r="E59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H59" s="7" t="n">
-        <v>399540</v>
-      </c>
-      <c r="I59" s="7" t="n">
-        <v>59931</v>
-      </c>
-      <c r="J59" s="7" t="n">
-        <v>339609</v>
-      </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="L59" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-23: Rs 12.0; 2025-10-27: Rs 5.0; 2025-09-19: Rs 14.5; 2025-04-25: Rs 10.0; 2025-02-21: Rs 12.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>GGL</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>Ghani Global Holdings Limited</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Miscellaneous</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="E60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr"/>
-      <c r="L60" s="8" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>TPL</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>TPL Corp Limited</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Technology &amp; Communication</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>14000</v>
-      </c>
-      <c r="E61" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="inlineStr"/>
-      <c r="L61" s="8" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>BFAGRO</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>Barkat Frisian Agro Limited</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Food &amp; Personal Care Products</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="n">
-        <v>17857</v>
-      </c>
-      <c r="E62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="inlineStr"/>
-      <c r="L62" s="8" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>ATLH</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Atlas Honda Limited</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>Automobile Assembler</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>12125</v>
-      </c>
-      <c r="E63" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="G63" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="H63" s="7" t="n">
-        <v>679000</v>
-      </c>
-      <c r="I63" s="7" t="n">
-        <v>101850</v>
-      </c>
-      <c r="J63" s="7" t="n">
-        <v>577150</v>
-      </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L63" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-30: Rs 56.0; 2025-10-30: Rs 46.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>PIOC</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>Pioneer Cement Limited</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Cement</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="n">
-        <v>123472</v>
-      </c>
-      <c r="E64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="L64" s="8" t="inlineStr">
-        <is>
-          <t>2025-09-29: Rs 5.0; 2025-02-28: Rs 5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>SRR</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Signature Residency Reit</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Real Estate Investment Trust</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>19829</v>
-      </c>
-      <c r="E65" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr"/>
-      <c r="L65" s="8" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="11" t="n">
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="11" t="n">
         <v>7898068</v>
       </c>
-      <c r="E66" s="10" t="n"/>
-      <c r="F66" s="10" t="n"/>
-      <c r="G66" s="10" t="n"/>
-      <c r="H66" s="12" t="n">
-        <v>56528163</v>
-      </c>
-      <c r="I66" s="12" t="n">
-        <v>8479224.449999999</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>48048938.55</v>
-      </c>
-      <c r="K66" s="10" t="n"/>
-      <c r="L66" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="10" t="n"/>
+      <c r="L42" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-10T10:44:17. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is the actual per-share cash dividend from the announcement(s) that triggered this update. Tax withheld at 15%.</t>
+          <t>Last updated 2026-07-10T10:48:52. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is the actual per-share cash dividend from the announcement(s) that triggered this update. Tax withheld at 15%.</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-04-23: Rs 9.0; 2025-10-22: Rs 9.0; 2025-08-06: Rs 9.0; 2025-04-23: Rs 9.0; 2025-02-06: Rs 9.0</t>
+          <t>2026-04-23: Rs 9.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-22: Rs 9.0; 2025-08-06: Rs 9.0; 2025-04-23: Rs 9.0; 2025-02-06: Rs 9.0</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>2026-04-17: Rs 6.0; 2026-02-18: Rs 6.0; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
+          <t>2026-04-17: Rs 6.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2026-02-18: Rs 6.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>2026-04-23: Rs 3.0; 2026-02-16: Rs 3.0; 2025-10-23: Rs 2.5; 2025-07-31: Rs 2.5; 2025-04-17: Rs 2.5; 2025-01-30: Rs 2.5</t>
+          <t>2026-04-23: Rs 3.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2026-02-16: Rs 3.0 [NEEDS REVIEW: no matching announcement PDF found]; 2025-10-23: Rs 2.5; 2025-07-31: Rs 2.5; 2025-04-17: Rs 2.5; 2025-01-30: Rs 2.5</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>2026-04-23: Rs 3.5; 2026-02-11: Rs 4.5; 2025-10-23: Rs 3.5; 2025-08-27: Rs 3.5; 2025-04-24: Rs 3.5; 2025-01-30: Rs 6.5</t>
+          <t>2026-04-23: Rs 3.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2026-02-11: Rs 4.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-23: Rs 3.5; 2025-08-27: Rs 3.5; 2025-04-24: Rs 3.5; 2025-01-30: Rs 6.5</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>2026-04-23: Rs 7.5; 2026-02-09: Rs 7.0; 2025-10-27: Rs 7.0; 2025-08-13: Rs 7.0; 2025-04-21: Rs 7.0; 2025-02-13: Rs 7.0</t>
+          <t>2026-04-23: Rs 7.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2026-02-09: Rs 7.0 [NEEDS REVIEW: no matching announcement PDF found]; 2025-10-27: Rs 7.0; 2025-08-13: Rs 7.0; 2025-04-21: Rs 7.0; 2025-02-13: Rs 7.0</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>2026-04-24: Rs 5.0; 2026-02-13: Rs 0.0; 2025-10-27: Rs 2.5; 2025-08-13: Rs 2.5; 2025-04-23: Rs 2.5; 2025-02-20: Rs 4.5</t>
+          <t>2026-04-24: Rs 5.0 [NEEDS REVIEW: could not parse period from PDF text]; 2026-02-13: Rs 0.0; 2025-10-27: Rs 2.5; 2025-08-13: Rs 2.5; 2025-04-23: Rs 2.5; 2025-02-20: Rs 4.5</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>2026-04-15: Rs 16.0; 2026-02-25: Rs 16.0; 2025-10-15: Rs 16.0; 2025-07-11: Rs 16.0; 2025-04-16: Rs 11.0; 2025-02-19: Rs 11.0</t>
+          <t>2026-04-15: Rs 16.0 [NEEDS REVIEW: unparseable period date ('Doctmbor 31,2025')]; 2026-02-25: Rs 16.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-15: Rs 16.0; 2025-07-11: Rs 16.0; 2025-04-16: Rs 11.0; 2025-02-19: Rs 11.0</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29: Rs 8.5; 2026-01-29: Rs 8.5; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
+          <t>2026-04-29: Rs 8.5 [NEEDS REVIEW: could not parse period from PDF text]; 2026-01-29: Rs 8.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29: Rs 2.0; 2026-02-13: Rs 2.0; 2025-10-29: Rs 2.0; 2025-09-19: Rs 2.5; 2025-04-29: Rs 1.0; 2025-02-28: Rs 2.0</t>
+          <t>2026-04-29: Rs 2.0 [NEEDS REVIEW: could not parse period from PDF text]; 2026-02-13: Rs 2.0 [FY2025 Final (excluded — not 2026)]; 2025-10-29: Rs 2.0; 2025-09-19: Rs 2.5; 2025-04-29: Rs 1.0; 2025-02-28: Rs 2.0</t>
         </is>
       </c>
     </row>
@@ -1319,27 +1319,19 @@
         <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.25</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>55250</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>8287.5</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>46962.5</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
@@ -1348,7 +1340,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29: Rs 3.25; 2026-02-23: Rs 4.25; 2025-10-29: Rs 3.5; 2025-09-23: Rs 5.0; 2025-04-30: Rs 3.0; 2025-02-28: Rs 0.0</t>
+          <t>2026-04-29: Rs 3.25 [Q1 2026 Interim]; 2026-02-23: Rs 4.25 [FY2025 Final (excluded — not 2026)]; 2025-10-29: Rs 3.5; 2025-09-23: Rs 5.0; 2025-04-30: Rs 3.0; 2025-02-28: Rs 0.0</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
@@ -1460,7 +1452,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>2026-04-28: Rs 1.5; 2025-04-25: Rs 2.0; 2024-11-13: Rs 5.0</t>
+          <t>2026-04-28: Rs 1.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-04-25: Rs 2.0; 2024-11-13: Rs 5.0</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
@@ -1516,7 +1508,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>2026-04-28: Rs 1.5; 2025-04-25: Rs 2.0; 2025-02-27: Rs 2.0</t>
+          <t>2026-04-28: Rs 1.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-04-25: Rs 2.0; 2025-02-27: Rs 2.0</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
@@ -1676,7 +1668,7 @@
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>2026-04-07: Rs 50.0; 2025-03-26: Rs 40.0</t>
+          <t>2026-04-07: Rs 50.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-03-26: Rs 40.0</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -1732,7 +1724,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24: Rs 6.0; 2025-08-27: Rs 2.0; 2025-02-28: Rs 4.0</t>
+          <t>2026-03-24: Rs 6.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-08-27: Rs 2.0; 2025-02-28: Rs 4.0</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
@@ -1788,7 +1780,7 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>2026-04-07: Rs 10.0; 2025-03-24: Rs 6.0</t>
+          <t>2026-04-07: Rs 10.0 [NEEDS REVIEW: no matching announcement PDF found]; 2025-03-24: Rs 6.0</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
@@ -1844,7 +1836,7 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>2026-02-18: Rs 2.0; 2025-08-28: Rs 2.0; 2025-03-04: Rs 1.5</t>
+          <t>2026-02-18: Rs 2.0 [NEEDS REVIEW: could not parse period from PDF text]; 2025-08-28: Rs 2.0; 2025-03-04: Rs 1.5</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
@@ -1900,7 +1892,7 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>2026-03-05: Rs 2.0; 2025-09-29: Rs 0.0</t>
+          <t>2026-03-05: Rs 2.0 [NEEDS REVIEW: no matching announcement PDF found]; 2025-09-29: Rs 0.0</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
@@ -2004,7 +1996,7 @@
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>2026-02-19: Rs 1.0; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
+          <t>2026-02-19: Rs 1.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
@@ -2108,7 +2100,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>2026-03-18: Rs 17.5; 2025-03-26: Rs 15.0</t>
+          <t>2026-03-18: Rs 17.5 [NEEDS REVIEW: could not parse period from PDF text]; 2025-03-26: Rs 15.0</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
@@ -2164,7 +2156,7 @@
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>2026-03-26: Rs 16.0; 2025-03-26: Rs 15.0</t>
+          <t>2026-03-26: Rs 16.0 [FY2025 Final (excluded — not 2026)]; 2025-03-26: Rs 15.0</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -2220,7 +2212,7 @@
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>2026-04-27: Rs 2.0; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
+          <t>2026-04-27: Rs 2.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
@@ -2276,7 +2268,7 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>2026-02-23: Rs 12.0; 2025-10-27: Rs 5.0; 2025-09-19: Rs 14.5; 2025-04-25: Rs 10.0; 2025-02-21: Rs 12.0</t>
+          <t>2026-02-23: Rs 12.0 [NEEDS REVIEW: no matching announcement PDF found]; 2025-10-27: Rs 5.0; 2025-09-19: Rs 14.5; 2025-04-25: Rs 10.0; 2025-02-21: Rs 12.0</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
@@ -2476,7 +2468,7 @@
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>2026-04-30: Rs 56.0; 2025-10-30: Rs 46.0</t>
+          <t>2026-04-30: Rs 56.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-30: Rs 46.0</t>
         </is>
       </c>
     </row>
@@ -2599,13 +2591,13 @@
       <c r="F42" s="10" t="n"/>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="12" t="n">
-        <v>0</v>
+        <v>55250</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0</v>
+        <v>8287.5</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>0</v>
+        <v>46962.5</v>
       </c>
       <c r="K42" s="10" t="n"/>
       <c r="L42" s="10" t="n"/>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-10T10:48:52. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is the actual per-share cash dividend from the announcement(s) that triggered this update. Tax withheld at 15%.</t>
+          <t>Last updated 2026-07-11T07:57:54. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is the actual per-share cash dividend from the announcement(s) that triggered this update. Tax withheld at 15%.</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>2026-04-23: Rs 9.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-22: Rs 9.0; 2025-08-06: Rs 9.0; 2025-04-23: Rs 9.0; 2025-02-06: Rs 9.0</t>
+          <t>2026-04-23: Rs 9.0 [Q1 2026 Interim]; 2025-10-22: Rs 9.0; 2025-08-06: Rs 9.0; 2025-04-23: Rs 9.0; 2025-02-06: Rs 9.0</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>2026-04-17: Rs 6.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2026-02-18: Rs 6.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
+          <t>2026-04-17: Rs 6.0 [Q1 2026 Interim]; 2026-02-18: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>2026-04-23: Rs 3.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2026-02-16: Rs 3.0 [NEEDS REVIEW: no matching announcement PDF found]; 2025-10-23: Rs 2.5; 2025-07-31: Rs 2.5; 2025-04-17: Rs 2.5; 2025-01-30: Rs 2.5</t>
+          <t>2026-04-23: Rs 3.0 [Q1 2026 Interim]; 2026-02-16: Rs 3.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 2.5; 2025-07-31: Rs 2.5; 2025-04-17: Rs 2.5; 2025-01-30: Rs 2.5</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>2026-04-23: Rs 3.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2026-02-11: Rs 4.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-23: Rs 3.5; 2025-08-27: Rs 3.5; 2025-04-24: Rs 3.5; 2025-01-30: Rs 6.5</t>
+          <t>2026-04-23: Rs 3.5 [Q1 2026 Interim]; 2026-02-11: Rs 4.5 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 3.5; 2025-08-27: Rs 3.5; 2025-04-24: Rs 3.5; 2025-01-30: Rs 6.5</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>2026-04-23: Rs 7.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2026-02-09: Rs 7.0 [NEEDS REVIEW: no matching announcement PDF found]; 2025-10-27: Rs 7.0; 2025-08-13: Rs 7.0; 2025-04-21: Rs 7.0; 2025-02-13: Rs 7.0</t>
+          <t>2026-04-23: Rs 7.5 [Q1 2026 Interim]; 2026-02-09: Rs 7.0 [FY2025 Final (excluded — not 2026)]; 2025-10-27: Rs 7.0; 2025-08-13: Rs 7.0; 2025-04-21: Rs 7.0; 2025-02-13: Rs 7.0</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>2026-04-24: Rs 5.0 [NEEDS REVIEW: could not parse period from PDF text]; 2026-02-13: Rs 0.0; 2025-10-27: Rs 2.5; 2025-08-13: Rs 2.5; 2025-04-23: Rs 2.5; 2025-02-20: Rs 4.5</t>
+          <t>2026-04-24: Rs 5.0 [Q1 2026 Interim]; 2026-02-13: Rs 0.0; 2025-10-27: Rs 2.5; 2025-08-13: Rs 2.5; 2025-04-23: Rs 2.5; 2025-02-20: Rs 4.5</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>2026-04-15: Rs 16.0 [NEEDS REVIEW: unparseable period date ('Doctmbor 31,2025')]; 2026-02-25: Rs 16.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-15: Rs 16.0; 2025-07-11: Rs 16.0; 2025-04-16: Rs 11.0; 2025-02-19: Rs 11.0</t>
+          <t>2026-04-15: Rs 16.0 [Q1 2026 Interim]; 2026-02-25: Rs 16.0 [FY2025 Final (excluded — not 2026)]; 2025-10-15: Rs 16.0; 2025-07-11: Rs 16.0; 2025-04-16: Rs 11.0; 2025-02-19: Rs 11.0</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29: Rs 8.5 [NEEDS REVIEW: could not parse period from PDF text]; 2026-01-29: Rs 8.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
+          <t>2026-04-29: Rs 8.5 [Q1 2026 Interim]; 2026-01-29: Rs 8.5 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>2026-04-29: Rs 2.0 [NEEDS REVIEW: could not parse period from PDF text]; 2026-02-13: Rs 2.0 [FY2025 Final (excluded — not 2026)]; 2025-10-29: Rs 2.0; 2025-09-19: Rs 2.5; 2025-04-29: Rs 1.0; 2025-02-28: Rs 2.0</t>
+          <t>2026-04-29: Rs 2.0 [FY2025 Final (excluded — not 2026)]; 2026-02-13: Rs 2.0 [FY2025 Final (excluded — not 2026)]; 2025-10-29: Rs 2.0; 2025-09-19: Rs 2.5; 2025-04-29: Rs 1.0; 2025-02-28: Rs 2.0</t>
         </is>
       </c>
     </row>
@@ -1321,17 +1321,25 @@
       <c r="F18" s="7" t="n">
         <v>3.25</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>55250</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>8287.5</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>46962.5</v>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
@@ -1423,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
@@ -1452,7 +1460,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>2026-04-28: Rs 1.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-04-25: Rs 2.0; 2024-11-13: Rs 5.0</t>
+          <t>2026-04-28: Rs 1.5 [Q1 2026 Interim]; 2025-04-25: Rs 2.0; 2024-11-13: Rs 5.0</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
@@ -1508,7 +1516,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>2026-04-28: Rs 1.5 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-04-25: Rs 2.0; 2025-02-27: Rs 2.0</t>
+          <t>2026-04-28: Rs 1.5 [Q1 2026 Interim]; 2025-04-25: Rs 2.0; 2025-02-27: Rs 2.0</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1676,7 @@
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>2026-04-07: Rs 50.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-03-26: Rs 40.0</t>
+          <t>2026-04-07: Rs 50.0 [FY2025 Final (excluded — not 2026)]; 2025-03-26: Rs 40.0</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>2026-03-24: Rs 6.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-08-27: Rs 2.0; 2025-02-28: Rs 4.0</t>
+          <t>2026-03-24: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-08-27: Rs 2.0; 2025-02-28: Rs 4.0</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1788,7 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>2026-04-07: Rs 10.0 [NEEDS REVIEW: no matching announcement PDF found]; 2025-03-24: Rs 6.0</t>
+          <t>2026-04-07: Rs 10.0 [FY2025 Final (excluded — not 2026)]; 2025-03-24: Rs 6.0</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1844,7 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>2026-02-18: Rs 2.0 [NEEDS REVIEW: could not parse period from PDF text]; 2025-08-28: Rs 2.0; 2025-03-04: Rs 1.5</t>
+          <t>2026-02-18: Rs 2.0 [FY2025 Final (excluded — not 2026)]; 2025-08-28: Rs 2.0; 2025-03-04: Rs 1.5</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2004,7 @@
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>2026-02-19: Rs 1.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
+          <t>2026-02-19: Rs 1.0 [FY2025 Final (excluded — not 2026)]; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2108,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>2026-03-18: Rs 17.5 [NEEDS REVIEW: could not parse period from PDF text]; 2025-03-26: Rs 15.0</t>
+          <t>2026-03-18: Rs 17.5 [FY2025 Final (excluded — not 2026)]; 2025-03-26: Rs 15.0</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -2212,7 +2220,7 @@
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>2026-04-27: Rs 2.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
+          <t>2026-04-27: Rs 2.0 [Q1 2026 Interim]; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2276,7 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>2026-02-23: Rs 12.0 [NEEDS REVIEW: no matching announcement PDF found]; 2025-10-27: Rs 5.0; 2025-09-19: Rs 14.5; 2025-04-25: Rs 10.0; 2025-02-21: Rs 12.0</t>
+          <t>2026-02-23: Rs 12.0 [FY2025 Final (excluded — not 2026)]; 2025-10-27: Rs 5.0; 2025-09-19: Rs 14.5; 2025-04-25: Rs 10.0; 2025-02-21: Rs 12.0</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
@@ -2468,7 +2476,7 @@
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>2026-04-30: Rs 56.0 [NEEDS REVIEW: scanned PDF, no extractable text]; 2025-10-30: Rs 46.0</t>
+          <t>2026-04-30: Rs 56.0 [FY2026 Final]; 2025-10-30: Rs 46.0</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2599,13 @@
       <c r="F42" s="10" t="n"/>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="12" t="n">
-        <v>55250</v>
+        <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>8287.5</v>
+        <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>46962.5</v>
+        <v>0</v>
       </c>
       <c r="K42" s="10" t="n"/>
       <c r="L42" s="10" t="n"/>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -493,11 +493,10 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,7 +509,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-11T07:57:54. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Dividend Announced is the actual per-share cash dividend from the announcement(s) that triggered this update. Tax withheld at 15%.</t>
+          <t>Last updated 2026-07-11T08:15:23. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026. Tax withheld at 15%.</t>
         </is>
       </c>
     </row>
@@ -547,30 +546,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Dividend Announced (PKR/share)</t>
+          <t>Gross Cash Dividend (PKR)</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Gross Cash Dividend (PKR)</t>
+          <t>Tax Amount (15%) (PKR)</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Tax Amount (15%) (PKR)</t>
+          <t>Net Cash Dividend (PKR)</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Net Cash Dividend (PKR)</t>
+          <t>Last Announcement Date</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Last Announcement Date</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Audit Log (Date: Amount/share)</t>
         </is>
@@ -601,32 +595,21 @@
       <c r="F5" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G5" s="7" t="n">
+        <v>3262545</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>489381.75</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>2773163.25</v>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>2026-04-23: Rs 9.0 [Q1 2026 Interim]; 2025-10-22: Rs 9.0; 2025-08-06: Rs 9.0; 2025-04-23: Rs 9.0; 2025-02-06: Rs 9.0</t>
         </is>
@@ -657,32 +640,21 @@
       <c r="F6" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G6" s="7" t="n">
+        <v>3998520</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>599778</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>3398742</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>2026-04-17: Rs 6.0 [Q1 2026 Interim]; 2026-02-18: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
         </is>
@@ -713,32 +685,21 @@
       <c r="F7" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G7" s="7" t="n">
+        <v>3934590</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>590188.5</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>3344401.5</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>2026-04-23: Rs 3.0 [Q1 2026 Interim]; 2026-02-16: Rs 3.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 2.5; 2025-07-31: Rs 2.5; 2025-04-17: Rs 2.5; 2025-01-30: Rs 2.5</t>
         </is>
@@ -769,32 +730,21 @@
       <c r="F8" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G8" s="7" t="n">
+        <v>5601043</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>840156.45</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>4760886.55</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>2026-04-23: Rs 3.5 [Q1 2026 Interim]; 2026-02-11: Rs 4.5 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 3.5; 2025-08-27: Rs 3.5; 2025-04-24: Rs 3.5; 2025-01-30: Rs 6.5</t>
         </is>
@@ -825,32 +775,21 @@
       <c r="F9" s="7" t="n">
         <v>7.5</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G9" s="7" t="n">
+        <v>602872.5</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>90430.875</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>512441.625</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>2026-04-23: Rs 7.5 [Q1 2026 Interim]; 2026-02-09: Rs 7.0 [FY2025 Final (excluded — not 2026)]; 2025-10-27: Rs 7.0; 2025-08-13: Rs 7.0; 2025-04-21: Rs 7.0; 2025-02-13: Rs 7.0</t>
         </is>
@@ -881,32 +820,21 @@
       <c r="F10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G10" s="7" t="n">
+        <v>3128435</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>469265.25</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>2659169.75</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>2026-04-24: Rs 5.0 [Q1 2026 Interim]; 2026-02-13: Rs 0.0; 2025-10-27: Rs 2.5; 2025-08-13: Rs 2.5; 2025-04-23: Rs 2.5; 2025-02-20: Rs 4.5</t>
         </is>
@@ -937,32 +865,21 @@
       <c r="F11" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G11" s="7" t="n">
+        <v>2820800</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>423120</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>2397680</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="L11" s="8" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>2026-04-15: Rs 16.0 [Q1 2026 Interim]; 2026-02-25: Rs 16.0 [FY2025 Final (excluded — not 2026)]; 2025-10-15: Rs 16.0; 2025-07-11: Rs 16.0; 2025-04-16: Rs 11.0; 2025-02-19: Rs 11.0</t>
         </is>
@@ -1010,15 +927,10 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>2025-08-11: Rs 20.0</t>
         </is>
@@ -1066,15 +978,10 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>2025-08-28: Rs 2.0</t>
         </is>
@@ -1122,15 +1029,10 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>2025-08-11: Rs 1.25</t>
         </is>
@@ -1176,13 +1078,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1209,32 +1106,21 @@
       <c r="F16" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G16" s="7" t="n">
+        <v>4956273.5</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>743441.025</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>4212832.475</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>2026-04-29: Rs 8.5 [Q1 2026 Interim]; 2026-01-29: Rs 8.5 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
         </is>
@@ -1282,15 +1168,10 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>2026-04-29: Rs 2.0 [FY2025 Final (excluded — not 2026)]; 2026-02-13: Rs 2.0 [FY2025 Final (excluded — not 2026)]; 2025-10-29: Rs 2.0; 2025-09-19: Rs 2.5; 2025-04-29: Rs 1.0; 2025-02-28: Rs 2.0</t>
         </is>
@@ -1321,32 +1202,21 @@
       <c r="F18" s="7" t="n">
         <v>3.25</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G18" s="7" t="n">
+        <v>55250</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>8287.5</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>46962.5</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>2026-04-29: Rs 3.25 [Q1 2026 Interim]; 2026-02-23: Rs 4.25 [FY2025 Final (excluded — not 2026)]; 2025-10-29: Rs 3.5; 2025-09-23: Rs 5.0; 2025-04-30: Rs 3.0; 2025-02-28: Rs 0.0</t>
         </is>
@@ -1394,15 +1264,10 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>2025-02-21: Rs 9.7</t>
         </is>
@@ -1433,32 +1298,21 @@
       <c r="F20" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="7" t="n">
+        <v>32037</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>4805.55</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>27231.45</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>2026-04-28: Rs 1.5 [Q1 2026 Interim]; 2025-04-25: Rs 2.0; 2024-11-13: Rs 5.0</t>
         </is>
@@ -1489,32 +1343,21 @@
       <c r="F21" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G21" s="7" t="n">
+        <v>46363.5</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>6954.525</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>39408.975</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>2026-04-28: Rs 1.5 [Q1 2026 Interim]; 2025-04-25: Rs 2.0; 2025-02-27: Rs 2.0</t>
         </is>
@@ -1560,13 +1403,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="8" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1610,15 +1448,10 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="L23" s="8" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>2025-08-28: Rs 3.5</t>
         </is>
@@ -1666,15 +1499,10 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="L24" s="8" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>2026-04-07: Rs 50.0 [FY2025 Final (excluded — not 2026)]; 2025-03-26: Rs 40.0</t>
         </is>
@@ -1722,15 +1550,10 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>2026-03-24: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-08-27: Rs 2.0; 2025-02-28: Rs 4.0</t>
         </is>
@@ -1778,15 +1601,10 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="L26" s="8" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>2026-04-07: Rs 10.0 [FY2025 Final (excluded — not 2026)]; 2025-03-24: Rs 6.0</t>
         </is>
@@ -1834,15 +1652,10 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>2026-02-18: Rs 2.0 [FY2025 Final (excluded — not 2026)]; 2025-08-28: Rs 2.0; 2025-03-04: Rs 1.5</t>
         </is>
@@ -1890,15 +1703,10 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr">
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>2026-03-05: Rs 2.0 [NEEDS REVIEW: no matching announcement PDF found]; 2025-09-29: Rs 0.0</t>
         </is>
@@ -1944,13 +1752,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="8" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1994,15 +1797,10 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>2026-02-19: Rs 1.0 [FY2025 Final (excluded — not 2026)]; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
         </is>
@@ -2048,13 +1846,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="8" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2098,15 +1891,10 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>2026-03-18: Rs 17.5 [FY2025 Final (excluded — not 2026)]; 2025-03-26: Rs 15.0</t>
         </is>
@@ -2154,15 +1942,10 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>2026-03-26: Rs 16.0 [FY2025 Final (excluded — not 2026)]; 2025-03-26: Rs 15.0</t>
         </is>
@@ -2193,32 +1976,21 @@
       <c r="F34" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G34" s="7" t="n">
+        <v>898000</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>134700</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>763300</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="L34" s="8" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>2026-04-27: Rs 2.0 [Q1 2026 Interim]; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
         </is>
@@ -2266,15 +2038,10 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="L35" s="8" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr">
         <is>
           <t>2026-02-23: Rs 12.0 [FY2025 Final (excluded — not 2026)]; 2025-10-27: Rs 5.0; 2025-09-19: Rs 14.5; 2025-04-25: Rs 10.0; 2025-02-21: Rs 12.0</t>
         </is>
@@ -2320,13 +2087,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="8" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -2368,13 +2130,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="8" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -2416,13 +2173,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="8" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2449,32 +2201,21 @@
       <c r="F39" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G39" s="7" t="n">
+        <v>679000</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>101850</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>577150</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="L39" s="8" t="inlineStr">
+      <c r="K39" s="8" t="inlineStr">
         <is>
           <t>2026-04-30: Rs 56.0 [FY2026 Final]; 2025-10-30: Rs 46.0</t>
         </is>
@@ -2522,15 +2263,10 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="L40" s="8" t="inlineStr">
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>2025-09-29: Rs 5.0; 2025-02-28: Rs 5.0</t>
         </is>
@@ -2576,13 +2312,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="8" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
@@ -2597,18 +2328,17 @@
       </c>
       <c r="E42" s="10" t="n"/>
       <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
+      <c r="G42" s="12" t="n">
+        <v>30015729.5</v>
+      </c>
       <c r="H42" s="12" t="n">
-        <v>0</v>
+        <v>4502359.425000001</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>0</v>
-      </c>
+        <v>25513370.075</v>
+      </c>
+      <c r="J42" s="10" t="n"/>
       <c r="K42" s="10" t="n"/>
-      <c r="L42" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -509,7 +509,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-11T08:15:23. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026. Tax withheld at 15%.</t>
+          <t>Last updated 2026-07-13T06:56:49. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026. Tax withheld at 15%.</t>
         </is>
       </c>
     </row>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,18 @@
       <name val="Arial"/>
       <i val="1"/>
       <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
       <sz val="9"/>
     </font>
     <font>
@@ -102,22 +114,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,1836 +523,1817 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-13T06:56:49. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026. Tax withheld at 15%.</t>
-        </is>
+          <t>Last updated 2026-07-13T07:02:24. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Tax Rate:</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Dividend This Month (PKR/share)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Dividend YTD 2026 (PKR/share)</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Gross Cash Dividend (PKR)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Tax Amount (15%) (PKR)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Net Cash Dividend (PKR)</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Last Announcement Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Audit Log (Date: Amount/share)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>MCB</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>MCB Bank Limited</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="n">
         <v>362505</v>
       </c>
-      <c r="E5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="n">
+      <c r="E5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>3262545</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>489381.75</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>2773163.25</v>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="G5" s="9">
+        <f>IF(F5=0,"-",D5*F5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="9">
+        <f>IF(F5=0,"-",G5*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I5" s="9">
+        <f>IF(F5=0,"-",G5-H5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>2026-04-23: Rs 9.0 [Q1 2026 Interim]; 2025-10-22: Rs 9.0; 2025-08-06: Rs 9.0; 2025-04-23: Rs 9.0; 2025-02-06: Rs 9.0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>HBL</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Habib Bank Limited</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="n">
         <v>666420</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="n">
+      <c r="E6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>3998520</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>599778</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>3398742</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="G6" s="9">
+        <f>IF(F6=0,"-",D6*F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="9">
+        <f>IF(F6=0,"-",G6*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I6" s="9">
+        <f>IF(F6=0,"-",G6-H6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>2026-04-17: Rs 6.0 [Q1 2026 Interim]; 2026-02-18: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>BAFL</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Bank Alfalah Limited</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="n">
         <v>1311530</v>
       </c>
-      <c r="E7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="n">
+      <c r="E7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>3934590</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>590188.5</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>3344401.5</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="G7" s="9">
+        <f>IF(F7=0,"-",D7*F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="9">
+        <f>IF(F7=0,"-",G7*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I7" s="9">
+        <f>IF(F7=0,"-",G7-H7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>2026-04-23: Rs 3.0 [Q1 2026 Interim]; 2026-02-16: Rs 3.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 2.5; 2025-07-31: Rs 2.5; 2025-04-17: Rs 2.5; 2025-01-30: Rs 2.5</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>BAHL</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Bank AL Habib Limited</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="n">
         <v>1600298</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="E8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>5601043</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>840156.45</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>4760886.55</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="G8" s="9">
+        <f>IF(F8=0,"-",D8*F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="9">
+        <f>IF(F8=0,"-",G8*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I8" s="9">
+        <f>IF(F8=0,"-",G8-H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>2026-04-23: Rs 3.5 [Q1 2026 Interim]; 2026-02-11: Rs 4.5 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 3.5; 2025-08-27: Rs 3.5; 2025-04-24: Rs 3.5; 2025-01-30: Rs 6.5</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>MEBL</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Meezan Bank Limited</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="n">
         <v>80383</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="n">
+      <c r="E9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>602872.5</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>90430.875</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>512441.625</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="G9" s="9">
+        <f>IF(F9=0,"-",D9*F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>IF(F9=0,"-",G9*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I9" s="9">
+        <f>IF(F9=0,"-",G9-H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>2026-04-23: Rs 7.5 [Q1 2026 Interim]; 2026-02-09: Rs 7.0 [FY2025 Final (excluded — not 2026)]; 2025-10-27: Rs 7.0; 2025-08-13: Rs 7.0; 2025-04-21: Rs 7.0; 2025-02-13: Rs 7.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>HMB</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Habib Metropolitan Bank Limited</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="n">
         <v>625687</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="n">
+      <c r="E10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>3128435</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>469265.25</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>2659169.75</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="G10" s="9">
+        <f>IF(F10=0,"-",D10*F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="9">
+        <f>IF(F10=0,"-",G10*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I10" s="9">
+        <f>IF(F10=0,"-",G10-H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>2026-04-24: Rs 5.0 [Q1 2026 Interim]; 2026-02-13: Rs 0.0; 2025-10-27: Rs 2.5; 2025-08-13: Rs 2.5; 2025-04-23: Rs 2.5; 2025-02-20: Rs 4.5</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>UBL</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>United Bank Limited</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="n">
         <v>176300</v>
       </c>
-      <c r="E11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="n">
+      <c r="E11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>2820800</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>423120</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>2397680</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="G11" s="9">
+        <f>IF(F11=0,"-",D11*F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="9">
+        <f>IF(F11=0,"-",G11*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I11" s="9">
+        <f>IF(F11=0,"-",G11-H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>2026-04-15: Rs 16.0 [Q1 2026 Interim]; 2026-02-25: Rs 16.0 [FY2025 Final (excluded — not 2026)]; 2025-10-15: Rs 16.0; 2025-07-11: Rs 16.0; 2025-04-16: Rs 11.0; 2025-02-19: Rs 11.0</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>LUCK</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Lucky Cement Limited</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="n">
         <v>24000</v>
       </c>
-      <c r="E12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="E12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <f>IF(F12=0,"-",D12*F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>IF(F12=0,"-",G12*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I12" s="9">
+        <f>IF(F12=0,"-",G12-H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>2025-08-11: Rs 20.0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>DGKC</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>D.G. Khan Cement Company Limited</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="n">
         <v>201936</v>
       </c>
-      <c r="E13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="E13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <f>IF(F13=0,"-",D13*F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="9">
+        <f>IF(F13=0,"-",G13*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I13" s="9">
+        <f>IF(F13=0,"-",G13-H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>2025-08-28: Rs 2.0</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>FCCL</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Fauji Cement Company Limited</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="n">
         <v>436625</v>
       </c>
-      <c r="E14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="E14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <f>IF(F14=0,"-",D14*F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="9">
+        <f>IF(F14=0,"-",G14*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I14" s="9">
+        <f>IF(F14=0,"-",G14-H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="K14" s="10" t="inlineStr">
         <is>
           <t>2025-08-11: Rs 1.25</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>MLCF</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Maple Leaf Cement Factory Limited</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="n">
         <v>110000</v>
       </c>
-      <c r="E15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <f>IF(F15=0,"-",D15*F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="9">
+        <f>IF(F15=0,"-",G15*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I15" s="9">
+        <f>IF(F15=0,"-",G15-H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>FFC</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Fauji Fertilizer Company Limited</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Fertilizers</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="n">
         <v>583091</v>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="7" t="n">
+      <c r="E16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>4956273.5</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>743441.025</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>4212832.475</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="G16" s="9">
+        <f>IF(F16=0,"-",D16*F16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="9">
+        <f>IF(F16=0,"-",G16*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I16" s="9">
+        <f>IF(F16=0,"-",G16-H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K16" s="10" t="inlineStr">
         <is>
           <t>2026-04-29: Rs 8.5 [Q1 2026 Interim]; 2026-01-29: Rs 8.5 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>PPL</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Pakistan Petroleum Limited</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>Oil/Gas</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="n">
         <v>20000</v>
       </c>
-      <c r="E17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="E17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <f>IF(F17=0,"-",D17*F17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="9">
+        <f>IF(F17=0,"-",G17*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I17" s="9">
+        <f>IF(F17=0,"-",G17-H17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>2026-04-29: Rs 2.0 [FY2025 Final (excluded — not 2026)]; 2026-02-13: Rs 2.0 [FY2025 Final (excluded — not 2026)]; 2025-10-29: Rs 2.0; 2025-09-19: Rs 2.5; 2025-04-29: Rs 1.0; 2025-02-28: Rs 2.0</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>OGDC</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Oil &amp; Gas Development Company Limited</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Oil/Gas</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="n">
         <v>17000</v>
       </c>
-      <c r="E18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="7" t="n">
+      <c r="E18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9" t="n">
         <v>3.25</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>55250</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>8287.5</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>46962.5</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="G18" s="9">
+        <f>IF(F18=0,"-",D18*F18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="9">
+        <f>IF(F18=0,"-",G18*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I18" s="9">
+        <f>IF(F18=0,"-",G18-H18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K18" s="10" t="inlineStr">
         <is>
           <t>2026-04-29: Rs 3.25 [Q1 2026 Interim]; 2026-02-23: Rs 4.25 [FY2025 Final (excluded — not 2026)]; 2025-10-29: Rs 3.5; 2025-09-23: Rs 5.0; 2025-04-30: Rs 3.0; 2025-02-28: Rs 0.0</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>ALTN</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Altern Energy Limited</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="n">
         <v>821</v>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="E19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <f>IF(F19=0,"-",D19*F19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="9">
+        <f>IF(F19=0,"-",G19*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I19" s="9">
+        <f>IF(F19=0,"-",G19-H19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>2025-02-21: Rs 9.7</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>NCPL</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Nishat Chunian Power Limited</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="n">
         <v>21358</v>
       </c>
-      <c r="E20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="7" t="n">
+      <c r="E20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G20" s="7" t="n">
-        <v>32037</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>4805.55</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>27231.45</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="G20" s="9">
+        <f>IF(F20=0,"-",D20*F20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="9">
+        <f>IF(F20=0,"-",G20*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I20" s="9">
+        <f>IF(F20=0,"-",G20-H20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>2026-04-28: Rs 1.5 [Q1 2026 Interim]; 2025-04-25: Rs 2.0; 2024-11-13: Rs 5.0</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>NPL</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Nishat Power Limited</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="n">
         <v>30909</v>
       </c>
-      <c r="E21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="7" t="n">
+      <c r="E21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>46363.5</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>6954.525</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>39408.975</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="G21" s="9">
+        <f>IF(F21=0,"-",D21*F21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="9">
+        <f>IF(F21=0,"-",G21*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I21" s="9">
+        <f>IF(F21=0,"-",G21-H21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>2026-04-28: Rs 1.5 [Q1 2026 Interim]; 2025-04-25: Rs 2.0; 2025-02-27: Rs 2.0</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>ASL</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Aisha Steel Mills Limited</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Steel Sector</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="n">
         <v>166000</v>
       </c>
-      <c r="E22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <f>IF(F22=0,"-",D22*F22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="9">
+        <f>IF(F22=0,"-",G22*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I22" s="9">
+        <f>IF(F22=0,"-",G22-H22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="7" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>AGIL</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Agriauto Industries Limited</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Others</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="n">
         <v>138635</v>
       </c>
-      <c r="E23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="E23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <f>IF(F23=0,"-",D23*F23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="9">
+        <f>IF(F23=0,"-",G23*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I23" s="9">
+        <f>IF(F23=0,"-",G23-H23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>2025-08-28: Rs 3.5</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>HINOON</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Highnoon Laboratories Limited</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="n">
         <v>7877</v>
       </c>
-      <c r="E24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="E24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <f>IF(F24=0,"-",D24*F24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="9">
+        <f>IF(F24=0,"-",G24*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I24" s="9">
+        <f>IF(F24=0,"-",G24-H24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>2026-04-07: Rs 50.0 [FY2025 Final (excluded — not 2026)]; 2025-03-26: Rs 40.0</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>AGP</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>AGP Limited</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="n">
         <v>39088</v>
       </c>
-      <c r="E25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="E25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <f>IF(F25=0,"-",D25*F25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="9">
+        <f>IF(F25=0,"-",G25*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I25" s="9">
+        <f>IF(F25=0,"-",G25-H25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>2026-03-24: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-08-27: Rs 2.0; 2025-02-28: Rs 4.0</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>SYS</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Systems Limited</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Tech</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="n">
         <v>101000</v>
       </c>
-      <c r="E26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="E26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <f>IF(F26=0,"-",D26*F26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="9">
+        <f>IF(F26=0,"-",G26*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I26" s="9">
+        <f>IF(F26=0,"-",G26-H26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>2026-04-07: Rs 10.0 [FY2025 Final (excluded — not 2026)]; 2025-03-24: Rs 6.0</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>AICL</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Adamjee Insurance Company Limited</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="n">
         <v>5000</v>
       </c>
-      <c r="E27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="E27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="9">
+        <f>IF(F27=0,"-",D27*F27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="9">
+        <f>IF(F27=0,"-",G27*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I27" s="9">
+        <f>IF(F27=0,"-",G27-H27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>2026-02-18: Rs 2.0 [FY2025 Final (excluded — not 2026)]; 2025-08-28: Rs 2.0; 2025-03-04: Rs 1.5</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>PTL</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Panther Tyres Ltd.</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Automobile Parts &amp; Accessories</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="n">
         <v>204610</v>
       </c>
-      <c r="E28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="E28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
+        <f>IF(F28=0,"-",D28*F28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="9">
+        <f>IF(F28=0,"-",G28*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I28" s="9">
+        <f>IF(F28=0,"-",G28-H28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="K28" s="8" t="inlineStr">
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>2026-03-05: Rs 2.0 [NEEDS REVIEW: no matching announcement PDF found]; 2025-09-29: Rs 0.0</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>BYCO</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Byco Petroleum Pakistan Limited</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Refinery</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <f>IF(F29=0,"-",D29*F29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="9">
+        <f>IF(F29=0,"-",G29*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I29" s="9">
+        <f>IF(F29=0,"-",G29-H29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>CPPL</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Cherat Packaging Limited</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Paper &amp; Board</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="n">
         <v>23655</v>
       </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="E30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <f>IF(F30=0,"-",D30*F30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="9">
+        <f>IF(F30=0,"-",G30*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I30" s="9">
+        <f>IF(F30=0,"-",G30-H30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>2026-02-19: Rs 1.0 [FY2025 Final (excluded — not 2026)]; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>FDIBL</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>First Dawood Investment Bank Limited</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Investment Banks / Companies</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="E31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9">
+        <f>IF(F31=0,"-",D31*F31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="9">
+        <f>IF(F31=0,"-",G31*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I31" s="9">
+        <f>IF(F31=0,"-",G31-H31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>SRVI</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Service Industries Limited</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Leather &amp; Tanneries</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="n">
         <v>23062</v>
       </c>
-      <c r="E32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="E32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <f>IF(F32=0,"-",D32*F32)</f>
+        <v/>
+      </c>
+      <c r="H32" s="9">
+        <f>IF(F32=0,"-",G32*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I32" s="9">
+        <f>IF(F32=0,"-",G32-H32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="K32" s="10" t="inlineStr">
         <is>
           <t>2026-03-18: Rs 17.5 [FY2025 Final (excluded — not 2026)]; 2025-03-26: Rs 15.0</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>PKGS</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Packages Limited</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Paper &amp; Board</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="E33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="9">
+        <f>IF(F33=0,"-",D33*F33)</f>
+        <v/>
+      </c>
+      <c r="H33" s="9">
+        <f>IF(F33=0,"-",G33*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I33" s="9">
+        <f>IF(F33=0,"-",G33-H33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="K33" s="10" t="inlineStr">
         <is>
           <t>2026-03-26: Rs 16.0 [FY2025 Final (excluded — not 2026)]; 2025-03-26: Rs 15.0</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>AKBL</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Askari Bank Limited</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="n">
         <v>449000</v>
       </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7" t="n">
+      <c r="E34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="7" t="n">
-        <v>898000</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>134700</v>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>763300</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="G34" s="9">
+        <f>IF(F34=0,"-",D34*F34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="9">
+        <f>IF(F34=0,"-",G34*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I34" s="9">
+        <f>IF(F34=0,"-",G34-H34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="K34" s="10" t="inlineStr">
         <is>
           <t>2026-04-27: Rs 2.0 [Q1 2026 Interim]; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>MUREB</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Murree Brewery Company Limited</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Food &amp; Personal Care Products</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="n">
         <v>33295</v>
       </c>
-      <c r="E35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="E35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="9">
+        <f>IF(F35=0,"-",D35*F35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="9">
+        <f>IF(F35=0,"-",G35*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I35" s="9">
+        <f>IF(F35=0,"-",G35-H35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>2026-02-23: Rs 12.0 [FY2025 Final (excluded — not 2026)]; 2025-10-27: Rs 5.0; 2025-09-19: Rs 14.5; 2025-04-25: Rs 10.0; 2025-02-21: Rs 12.0</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>GGL</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Ghani Global Holdings Limited</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Miscellaneous</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="n">
         <v>250000</v>
       </c>
-      <c r="E36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="8" t="inlineStr"/>
+      <c r="E36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9">
+        <f>IF(F36=0,"-",D36*F36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="9">
+        <f>IF(F36=0,"-",G36*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I36" s="9">
+        <f>IF(F36=0,"-",G36-H36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>TPL</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>TPL Corp Limited</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Technology &amp; Communication</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="n">
         <v>14000</v>
       </c>
-      <c r="E37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="8" t="inlineStr"/>
+      <c r="E37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="9">
+        <f>IF(F37=0,"-",D37*F37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="9">
+        <f>IF(F37=0,"-",G37*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I37" s="9">
+        <f>IF(F37=0,"-",G37-H37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>BFAGRO</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Barkat Frisian Agro Limited</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Food &amp; Personal Care Products</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="n">
         <v>17857</v>
       </c>
-      <c r="E38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="8" t="inlineStr"/>
+      <c r="E38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <f>IF(F38=0,"-",D38*F38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="9">
+        <f>IF(F38=0,"-",G38*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I38" s="9">
+        <f>IF(F38=0,"-",G38-H38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="7" t="inlineStr"/>
+      <c r="K38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>ATLH</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Atlas Honda Limited</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Automobile Assembler</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="n">
         <v>12125</v>
       </c>
-      <c r="E39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="7" t="n">
+      <c r="E39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="G39" s="7" t="n">
-        <v>679000</v>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>101850</v>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>577150</v>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="G39" s="9">
+        <f>IF(F39=0,"-",D39*F39)</f>
+        <v/>
+      </c>
+      <c r="H39" s="9">
+        <f>IF(F39=0,"-",G39*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I39" s="9">
+        <f>IF(F39=0,"-",G39-H39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K39" s="8" t="inlineStr">
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>2026-04-30: Rs 56.0 [FY2026 Final]; 2025-10-30: Rs 46.0</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>PIOC</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Pioneer Cement Limited</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="n">
         <v>123472</v>
       </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="E40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="9">
+        <f>IF(F40=0,"-",D40*F40)</f>
+        <v/>
+      </c>
+      <c r="H40" s="9">
+        <f>IF(F40=0,"-",G40*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I40" s="9">
+        <f>IF(F40=0,"-",G40-H40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="K40" s="8" t="inlineStr">
+      <c r="K40" s="10" t="inlineStr">
         <is>
           <t>2025-09-29: Rs 5.0; 2025-02-28: Rs 5.0</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>SRR</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Signature Residency Reit</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Real Estate Investment Trust</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="n">
         <v>19829</v>
       </c>
-      <c r="E41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="8" t="inlineStr"/>
+      <c r="E41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="9">
+        <f>IF(F41=0,"-",D41*F41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="9">
+        <f>IF(F41=0,"-",G41*$B$3)</f>
+        <v/>
+      </c>
+      <c r="I41" s="9">
+        <f>IF(F41=0,"-",G41-H41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="11" t="n">
-        <v>7898068</v>
-      </c>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="12" t="n">
-        <v>30015729.5</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>4502359.425000001</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>25513370.075</v>
-      </c>
-      <c r="J42" s="10" t="n"/>
-      <c r="K42" s="10" t="n"/>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="13">
+        <f>SUM(D5:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="14">
+        <f>SUM(G5:G41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="14">
+        <f>SUM(H5:H41)</f>
+        <v/>
+      </c>
+      <c r="I42" s="14">
+        <f>SUM(I5:I41)</f>
+        <v/>
+      </c>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -495,7 +495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-10T07:40:40. Source: PSX company payout announcements (board-meeting/announcement date).</t>
+          <t>Last updated 2026-07-22T15:24:46. Source: PSX company payout announcements (board-meeting/announcement date).</t>
         </is>
       </c>
     </row>
@@ -716,14 +716,14 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1842,128 +1842,128 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>AVN</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>April 30, 2026 2:53 PM</t>
+          <t>July 22, 2026 3:47 PM</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>30/06/2026(HYR)</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>10%(F) (D)</t>
+          <t>160%(ii) (D)</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>AVN</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2026 2:58 PM</t>
+          <t>April 30, 2026 2:53 PM</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>85%(i) (D)</t>
+          <t>10%(F) (D)</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="G3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2026 3:18 PM</t>
+          <t>April 29, 2026 2:58 PM</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>20%(iii) (D)</t>
+          <t>85%(i) (D)</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="G4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2026 3:56 PM</t>
+          <t>April 29, 2026 3:18 PM</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IIIQ)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>32.50%(iii) (D)</t>
+          <t>20%(iii) (D)</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="G5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2026 4:03 PM</t>
+          <t>April 29, 2026 3:56 PM</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1973,26 +1973,26 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>15%(i) (D)</t>
+          <t>32.50%(iii) (D)</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="G6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2026 4:02 PM</t>
+          <t>April 28, 2026 4:03 PM</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2016,12 +2016,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>April 27, 2026 3:50 PM</t>
+          <t>April 28, 2026 4:02 PM</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2031,26 +2031,26 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>510%(iii) (D)</t>
+          <t>15%(i) (D)</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>51</v>
+        <v>1.5</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>51</v>
+        <v>1.5</v>
       </c>
       <c r="G8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>OLPL</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>April 27, 2026 3:57 PM</t>
+          <t>April 27, 2026 3:50 PM</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2060,84 +2060,84 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>510%(iii) (D)</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>OLPL</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>April 24, 2026 4:35 PM</t>
+          <t>April 27, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ) - 31/03/2026(IQ)</t>
+          <t>31/03/2026(IIIQ)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>25%(i) (D)  -  25%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 3:56 PM</t>
+          <t>April 24, 2026 4:35 PM</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>31/03/2026(IQ) - 31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>90%(i) (D)</t>
+          <t>25%(i) (D)  -  25%(i) (D)</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 3:49 PM</t>
+          <t>April 23, 2026 3:56 PM</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -2147,26 +2147,26 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>30%(i) (D)</t>
+          <t>90%(i) (D)</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 4:04 PM</t>
+          <t>April 23, 2026 3:49 PM</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2176,26 +2176,26 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>30%(i) (D)</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 3:51 PM</t>
+          <t>April 23, 2026 4:04 PM</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -2205,55 +2205,55 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>75%(i) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="G14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>April 22, 2026 12:35 PM</t>
+          <t>April 23, 2026 3:51 PM</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IIIQ)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>50%(iii) (D)</t>
+          <t>75%(i) (D)</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="G15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>April 20, 2026 3:41 PM</t>
+          <t>April 22, 2026 12:35 PM</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -2263,55 +2263,55 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>50%(iii) (D)</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>April 17, 2026 5:10 PM</t>
+          <t>April 20, 2026 3:41 PM</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>31/03/2026(IIIQ)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>60%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>April 15, 2026 3:51 PM</t>
+          <t>April 17, 2026 5:10 PM</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2321,55 +2321,55 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>160%(i) (D)</t>
+          <t>60%(i) (D)</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>HINOON</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>April 7, 2026 4:00 PM</t>
+          <t>April 15, 2026 3:51 PM</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>500%(F) (D)</t>
+          <t>160%(i) (D)</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="G19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>SYS</t>
+          <t>HINOON</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>April 7, 2026 3:57 PM</t>
+          <t>April 7, 2026 4:00 PM</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2379,26 +2379,26 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>500%(F) (D)</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>SYS</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>March 26, 2026 3:54 PM</t>
+          <t>April 7, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2408,26 +2408,26 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>120%(F) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>AGP</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>March 24, 2026 4:16 PM</t>
+          <t>March 26, 2026 3:54 PM</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2437,26 +2437,26 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>60%(F) (D)</t>
+          <t>120%(F) (D)</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>ABOT</t>
+          <t>AGP</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>March 16, 2026 2:30 PM</t>
+          <t>March 24, 2026 4:16 PM</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2466,26 +2466,26 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>400%(F) (D)</t>
+          <t>60%(F) (D)</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="G23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>ABOT</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>March 9, 2026 2:14 PM</t>
+          <t>March 16, 2026 2:30 PM</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2495,26 +2495,26 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>400%(F) (D)</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2.5</v>
+        <v>40</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>2.5</v>
+        <v>40</v>
       </c>
       <c r="G24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>February 25, 2026 12:28 PM</t>
+          <t>March 9, 2026 2:14 PM</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2524,55 +2524,55 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>160%(F) (D)</t>
+          <t>25%(F) (D)</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="G25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>February 24, 2026 2:17 PM</t>
+          <t>February 25, 2026 12:28 PM</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>275%(i) (D)</t>
+          <t>160%(F) (D)</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>27.5</v>
+        <v>16</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>27.5</v>
+        <v>16</v>
       </c>
       <c r="G26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>February 24, 2026 2:38 PM</t>
+          <t>February 24, 2026 2:17 PM</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -2582,26 +2582,26 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>50%(ii) (D)</t>
+          <t>275%(i) (D)</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>5</v>
+        <v>27.5</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>5</v>
+        <v>27.5</v>
       </c>
       <c r="G27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>February 23, 2026 1:25 PM</t>
+          <t>February 24, 2026 2:38 PM</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2611,26 +2611,26 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>42.50%(ii) (D)</t>
+          <t>50%(ii) (D)</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="G28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>February 23, 2026 1:14 PM</t>
+          <t>February 23, 2026 1:25 PM</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2640,113 +2640,113 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>460%(ii) (D)</t>
+          <t>42.50%(ii) (D)</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>46</v>
+        <v>4.25</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>46</v>
+        <v>4.25</v>
       </c>
       <c r="G29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>February 18, 2026 3:51 PM</t>
+          <t>February 23, 2026 1:14 PM</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>60%(F) (D)</t>
+          <t>460%(ii) (D)</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>CHCC</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>February 18, 2026 3:39 PM</t>
+          <t>February 18, 2026 3:51 PM</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>15%(i) (D)</t>
+          <t>60%(F) (D)</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="G31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>CHCC</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>February 16, 2026 4:25 PM</t>
+          <t>February 18, 2026 3:39 PM</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>30%(F) (D)</t>
+          <t>15%(i) (D)</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>February 13, 2026 3:57 PM</t>
+          <t>February 16, 2026 4:25 PM</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -2756,84 +2756,84 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>45%F) (D)</t>
+          <t>30%(F) (D)</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>February 13, 2026 4:00 PM</t>
+          <t>February 13, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>20%(F) (D)</t>
+          <t>45%F) (D)</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>February 12, 2026 3:27 PM</t>
+          <t>February 13, 2026 4:00 PM</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>20%(F) (D)</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>February 11, 2026 3:57 PM</t>
+          <t>February 12, 2026 3:27 PM</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2843,26 +2843,26 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>45%(F) (D)</t>
+          <t>40%(F) (D)</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>February 9, 2026 3:36 PM</t>
+          <t>February 11, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2872,26 +2872,26 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>70%(F) (D)</t>
+          <t>45%(F) (D)</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="G37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>January 29, 2026 3:14 PM</t>
+          <t>February 9, 2026 3:36 PM</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2901,113 +2901,113 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>85%(F) (D)</t>
+          <t>70%(F) (D)</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="G38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>January 27, 2026 4:55 PM</t>
+          <t>January 29, 2026 3:14 PM</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>85%(F) (D)</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="G39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>MARI</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>January 26, 2026 4:05 PM</t>
+          <t>January 27, 2026 4:55 PM</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>30/09/2025(HYR)</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>83%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>2</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>2</v>
       </c>
       <c r="G40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>MARI</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>October 30, 2025 4:28 PM</t>
+          <t>January 26, 2026 4:05 PM</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IQ)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>50%(i) (D)</t>
+          <t>83%(i) (D)</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>October 29, 2025 3:14 PM</t>
+          <t>October 30, 2025 4:28 PM</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -3017,26 +3017,26 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>50%(i) (D)</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>October 29, 2025 4:08 PM</t>
+          <t>October 29, 2025 3:14 PM</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -3046,26 +3046,26 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="G43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>October 28, 2025 4:40 PM</t>
+          <t>October 29, 2025 4:08 PM</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -3075,55 +3075,55 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>510%(i) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>51</v>
+        <v>3.5</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>51</v>
+        <v>3.5</v>
       </c>
       <c r="G44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>October 27, 2025 11:09 AM</t>
+          <t>October 28, 2025 4:40 PM</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>30/09/2025(IQ)</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>70%(iii) (D)</t>
+          <t>510%(i) (D)</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>October 27, 2025 11:03 AM</t>
+          <t>October 27, 2025 11:09 AM</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -3133,26 +3133,26 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>25%(iii) (D)</t>
+          <t>70%(iii) (D)</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:48 PM</t>
+          <t>October 27, 2025 11:03 AM</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -3162,26 +3162,26 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>50%(iii) (D)</t>
+          <t>25%(iii) (D)</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:27 PM</t>
+          <t>October 23, 2025 3:48 PM</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -3191,26 +3191,26 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>25%(iii) (D)</t>
+          <t>50%(iii) (D)</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:50 PM</t>
+          <t>October 23, 2025 3:27 PM</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -3220,26 +3220,26 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>35%(iii) (D)</t>
+          <t>25%(iii) (D)</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:41 PM</t>
+          <t>October 23, 2025 3:50 PM</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3249,26 +3249,26 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>95%(iii) (D)</t>
+          <t>35%(iii) (D)</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="G50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>October 22, 2025 3:42 PM</t>
+          <t>October 23, 2025 3:41 PM</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3278,26 +3278,26 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>90%(iii) (D)</t>
+          <t>95%(iii) (D)</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>October 15, 2025 3:53 PM</t>
+          <t>October 22, 2025 3:42 PM</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3307,26 +3307,26 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>160%(iii) (D)</t>
+          <t>90%(iii) (D)</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>October 15, 2025 3:50 PM</t>
+          <t>October 15, 2025 3:53 PM</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3336,55 +3336,55 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>45%(iii) (D)</t>
+          <t>160%(iii) (D)</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="G53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>CPHL</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>October 2, 2025 4:35 PM</t>
+          <t>October 15, 2025 3:50 PM</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>35%(F) (D)</t>
+          <t>45%(iii) (D)</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>NML</t>
+          <t>CPHL</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>September 30, 2025 3:34 PM</t>
+          <t>October 2, 2025 4:35 PM</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -3394,26 +3394,26 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>20%(F) (D)</t>
+          <t>35%(F) (D)</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>OLPL</t>
+          <t>NML</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>September 25, 2025 4:24 PM</t>
+          <t>September 30, 2025 3:34 PM</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -3423,26 +3423,26 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>35%(F) (D)</t>
+          <t>20%(F) (D)</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="G56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>OLPL</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>September 23, 2025 4:03 PM</t>
+          <t>September 25, 2025 4:24 PM</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -3452,26 +3452,26 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>50%(F) (D)</t>
+          <t>35%(F) (D)</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="G57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>FEROZ</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>September 23, 2025 4:40 PM</t>
+          <t>September 23, 2025 4:03 PM</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -3481,26 +3481,26 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>50%(F) (D)</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>FEROZ</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>September 19, 2025 4:11 PM</t>
+          <t>September 23, 2025 4:40 PM</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -3510,26 +3510,26 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>40%(F) (D)</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="G59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>September 3, 2025 3:56 PM</t>
+          <t>September 19, 2025 4:11 PM</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -3539,26 +3539,26 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>25%(F) (D)</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="G60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>August 29, 2025 5:08 PM</t>
+          <t>September 3, 2025 3:56 PM</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -3568,26 +3568,26 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>500%(F) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>DGKC</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>August 28, 2025 4:47 PM</t>
+          <t>August 29, 2025 5:08 PM</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -3597,26 +3597,26 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>20%(F) (D)</t>
+          <t>500%(F) (D)</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>AGIL</t>
+          <t>DGKC</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>August 28, 2025 4:44 PM</t>
+          <t>August 28, 2025 4:47 PM</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3626,36 +3626,36 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>35%(F) (D)</t>
+          <t>20%(F) (D)</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="G63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>AGIL</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>August 27, 2025 4:33 PM</t>
+          <t>August 28, 2025 4:44 PM</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>35%(ii) (D)</t>
+          <t>35%(F) (D)</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
@@ -3669,12 +3669,12 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>August 27, 2025 4:34 PM</t>
+          <t>August 27, 2025 4:33 PM</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>35%(ii) (D)</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -3698,12 +3698,12 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>AGP</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>August 27, 2025 3:59 PM</t>
+          <t>August 27, 2025 4:34 PM</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -3713,26 +3713,26 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>AGP</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>August 26, 2025 3:34 PM</t>
+          <t>August 27, 2025 3:59 PM</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -3742,55 +3742,55 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>50%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>CHCC</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>August 21, 2025 3:53 PM</t>
+          <t>August 26, 2025 3:34 PM</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>50%(i) (D)</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>CHCC</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>August 20, 2025 3:40 PM</t>
+          <t>August 21, 2025 3:53 PM</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -3800,26 +3800,26 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>40%(F) (D)</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="G69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>PSO</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>August 19, 2025 4:17 PM</t>
+          <t>August 20, 2025 3:40 PM</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -3829,55 +3829,55 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>25%(F) (D)</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="G70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>PSO</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>August 13, 2025 3:40 PM</t>
+          <t>August 19, 2025 4:17 PM</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>70%(ii) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>August 13, 2025 3:38 PM</t>
+          <t>August 13, 2025 3:40 PM</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -3887,55 +3887,55 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>25%(ii) (D)</t>
+          <t>70%(ii) (D)</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="G72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>LUCK</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 11:11 AM</t>
+          <t>August 13, 2025 3:38 PM</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>200%(F) (D)</t>
+          <t>25%(ii) (D)</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>FCCL</t>
+          <t>LUCK</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 11:05 AM</t>
+          <t>August 11, 2025 11:11 AM</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -3945,26 +3945,26 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>12.50%(F) (D)</t>
+          <t>200%(F) (D)</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1.25</v>
+        <v>20</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>1.25</v>
+        <v>20</v>
       </c>
       <c r="G74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>FCCL</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 3:29 PM</t>
+          <t>August 11, 2025 11:05 AM</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -3974,26 +3974,26 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>500%(F) (D)</t>
+          <t>12.50%(F) (D)</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>50</v>
+        <v>1.25</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>50</v>
+        <v>1.25</v>
       </c>
       <c r="G75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>MARI</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 10:57 AM</t>
+          <t>August 11, 2025 3:29 PM</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -4003,55 +4003,55 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>217%(F) (D)</t>
+          <t>500%(F) (D)</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>21.7</v>
+        <v>50</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>21.7</v>
+        <v>50</v>
       </c>
       <c r="G76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>MARI</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>August 6, 2025 3:49 PM</t>
+          <t>August 11, 2025 10:57 AM</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>90%(ii) (D)</t>
+          <t>217%(F) (D)</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>9</v>
+        <v>21.7</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>9</v>
+        <v>21.7</v>
       </c>
       <c r="G77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>July 31, 2025 3:49 PM</t>
+          <t>August 6, 2025 3:49 PM</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -4061,26 +4061,26 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>45%(ii) (D)</t>
+          <t>90%(ii) (D)</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="G78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>July 31, 2025 3:53 PM</t>
+          <t>July 31, 2025 3:49 PM</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -4090,26 +4090,26 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>25%(ii) (D)</t>
+          <t>45%(ii) (D)</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>July 30, 2025 3:24 PM</t>
+          <t>July 31, 2025 3:53 PM</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -4119,26 +4119,26 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>42.50%(ii) (D)</t>
+          <t>25%(ii) (D)</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="G80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>July 29, 2025 3:26 PM</t>
+          <t>July 30, 2025 3:24 PM</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -4148,26 +4148,26 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>120%(ii) (D)</t>
+          <t>42.50%(ii) (D)</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>12</v>
+        <v>4.25</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>12</v>
+        <v>4.25</v>
       </c>
       <c r="G81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>July 11, 2025 5:05 PM</t>
+          <t>July 29, 2025 3:26 PM</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -4177,55 +4177,55 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>160%(II) (D)</t>
+          <t>120%(ii) (D)</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>April 30, 2025 4:16 PM</t>
+          <t>July 11, 2025 5:05 PM</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>30%(iii) (D)</t>
+          <t>160%(II) (D)</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2025 2:46 PM</t>
+          <t>April 30, 2025 4:16 PM</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -4235,142 +4235,142 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>10%(iii) (D)</t>
+          <t>30%(iii) (D)</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2025 3:39 PM</t>
+          <t>April 29, 2025 2:46 PM</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>70%(i) (D)</t>
+          <t>10%(iii) (D)</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2025 12:00 PM</t>
+          <t>April 28, 2025 3:39 PM</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>500%(iii) (D)</t>
+          <t>70%(i) (D)</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="G86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>April 25, 2025 4:31 PM</t>
+          <t>April 28, 2025 12:00 PM</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>45%(i) (D)</t>
+          <t>500%(iii) (D)</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>4.5</v>
+        <v>50</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>4.5</v>
+        <v>50</v>
       </c>
       <c r="G87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>April 25, 2025 5:30 PM</t>
+          <t>April 25, 2025 4:31 PM</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>20%(iii) (D)</t>
+          <t>45%(i) (D)</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="G88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>April 25, 2025 5:26 PM</t>
+          <t>April 25, 2025 5:30 PM</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -4394,99 +4394,99 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>April 24, 2025 4:02 PM</t>
+          <t>April 25, 2025 5:26 PM</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>20%(iii) (D)</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="G90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>OLPL</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>April 24, 2025 12:45 PM</t>
+          <t>April 24, 2025 4:02 PM</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>OLPL</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2025 3:39 PM</t>
+          <t>April 24, 2025 12:45 PM</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>90%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2025 3:22 PM</t>
+          <t>April 23, 2025 3:39 PM</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -4496,26 +4496,26 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>25%(i) (D)</t>
+          <t>90%(i) (D)</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="G93" s="7" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>April 22, 2025 5:01 PM</t>
+          <t>April 23, 2025 3:22 PM</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -4525,26 +4525,26 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>22.5%(i) (D)</t>
+          <t>25%(i) (D)</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="G94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>April 21, 2025 4:10 PM</t>
+          <t>April 22, 2025 5:01 PM</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -4554,26 +4554,26 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>70%(i) (D)</t>
+          <t>22.5%(i) (D)</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>7</v>
+        <v>2.25</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>7</v>
+        <v>2.25</v>
       </c>
       <c r="G95" s="7" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>April 17, 2025 3:56 PM</t>
+          <t>April 21, 2025 4:10 PM</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -4583,26 +4583,26 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>25%(i) (D)</t>
+          <t>70%(i) (D)</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="G96" s="7" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>April 16, 2025 4:52 PM</t>
+          <t>April 17, 2025 3:56 PM</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -4612,55 +4612,55 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>110%(i) (D)</t>
+          <t>25%(i) (D)</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="G97" s="7" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>HINOON</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>March 26, 2025 2:45 PM</t>
+          <t>April 16, 2025 4:52 PM</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>400%(F) (D)</t>
+          <t>110%(i) (D)</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>HINOON</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>March 24, 2025 2:13 PM</t>
+          <t>March 26, 2025 2:45 PM</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -4670,26 +4670,26 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>400%(F) (D)</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G99" s="7" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>SYS</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>March 24, 2025 2:14 PM</t>
+          <t>March 24, 2025 2:13 PM</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -4699,26 +4699,26 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>60%(F) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>SYS</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>March 14, 2025 1:12 PM</t>
+          <t>March 24, 2025 2:14 PM</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -4728,55 +4728,55 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>42.5%(F) (D)</t>
+          <t>60%(F) (D)</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>4.25</v>
+        <v>6</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>4.25</v>
+        <v>6</v>
       </c>
       <c r="G101" s="7" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 4:26 PM</t>
+          <t>March 14, 2025 1:12 PM</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/12/2024(YR)</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>20%(ii) (D)</t>
+          <t>42.5%(F) (D)</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="G102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 4:32 PM</t>
+          <t>February 28, 2025 4:26 PM</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -4786,26 +4786,26 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>40.50% (D)</t>
+          <t>20%(ii) (D)</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 10:58 AM</t>
+          <t>February 28, 2025 4:32 PM</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -4815,84 +4815,84 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>370%(ii) (D)</t>
+          <t>40.50% (D)</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>AGP</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 11:04 AM</t>
+          <t>February 28, 2025 10:58 AM</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/12/2024(HYR)</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>370%(ii) (D)</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="G105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>AGP</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>February 27, 2025 2:56 PM</t>
+          <t>February 28, 2025 11:04 AM</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/12/2024(YR)</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>40%(F) (D)</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>February 26, 2025 12:53 PM</t>
+          <t>February 27, 2025 2:56 PM</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
@@ -4902,26 +4902,26 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>50%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>CHCC</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>February 21, 2025 2:43 PM</t>
+          <t>February 26, 2025 12:53 PM</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -4931,84 +4931,84 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>15%(i) (D)</t>
+          <t>50%(i) (D)</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="G108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>ALTN</t>
+          <t>CHCC</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>February 21, 2025 5:00 PM</t>
+          <t>February 21, 2025 2:43 PM</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31/12/2024(HYR)</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>97%(i) (D)</t>
+          <t>15%(i) (D)</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="G109" s="7" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>ALTN</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>February 20, 2025 3:24 PM</t>
+          <t>February 21, 2025 5:00 PM</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>45%(F) (D)</t>
+          <t>97%(i) (D)</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>4.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G110" s="7" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>ABOT</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>February 20, 2025 3:45 PM</t>
+          <t>February 20, 2025 3:24 PM</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -5018,26 +5018,26 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>45%(F) (D)</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="G111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>ABOT</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>February 19, 2025 3:45 PM</t>
+          <t>February 20, 2025 3:45 PM</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -5047,26 +5047,26 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>42.5%(F) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>4.25</v>
+        <v>10</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>4.25</v>
+        <v>10</v>
       </c>
       <c r="G112" s="7" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>February 19, 2025 3:42 PM</t>
+          <t>February 19, 2025 3:45 PM</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
@@ -5076,26 +5076,26 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>110%(F) (D)</t>
+          <t>42.5%(F) (D)</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>11</v>
+        <v>4.25</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>11</v>
+        <v>4.25</v>
       </c>
       <c r="G113" s="7" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>February 13, 2025 3:30 PM</t>
+          <t>February 19, 2025 3:42 PM</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -5105,26 +5105,26 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>70%(F) (D)</t>
+          <t>110%(F) (D)</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>February 10, 2025 3:39 PM</t>
+          <t>February 13, 2025 3:30 PM</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -5134,26 +5134,26 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>80%(F) (D)</t>
+          <t>70%(F) (D)</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>February 6, 2025 4:25 PM</t>
+          <t>February 10, 2025 3:39 PM</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -5163,26 +5163,26 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>90%(F) (D)</t>
+          <t>80%(F) (D)</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>January 30, 2025 4:00 PM</t>
+          <t>February 6, 2025 4:25 PM</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
@@ -5192,26 +5192,26 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>90%(F) (D)</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="G117" s="7" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>January 30, 2025 4:05 PM</t>
+          <t>January 30, 2025 4:00 PM</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -5221,26 +5221,26 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>65%(F) (D)</t>
+          <t>25%(F) (D)</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="G118" s="7" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>January 29, 2025 3:36 PM</t>
+          <t>January 30, 2025 4:05 PM</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
@@ -5250,74 +5250,103 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>210%(F) (D)</t>
+          <t>65%(F) (D)</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>21</v>
+        <v>6.5</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>21</v>
+        <v>6.5</v>
       </c>
       <c r="G119" s="7" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>January 27, 2025 4:28 PM</t>
+          <t>January 29, 2025 3:36 PM</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/12/2024(YR)</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>250%(i) (D)</t>
+          <t>210%(F) (D)</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G120" s="7" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>January 27, 2025 4:28 PM</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(HYR)</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>250%(i) (D)</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
           <t>NCPL</t>
         </is>
       </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B122" s="5" t="inlineStr">
         <is>
           <t>November 13, 2024 4:33 PM</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C122" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>50%(I) (D)</t>
         </is>
       </c>
-      <c r="E121" s="5" t="n">
+      <c r="E122" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F121" s="5" t="n">
+      <c r="F122" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G121" s="7" t="inlineStr"/>
+      <c r="G122" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-13T07:02:24. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+          <t>Last updated 2026-08-01T12:12:24. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>2026-04-23: Rs 9.0 [Q1 2026 Interim]; 2025-10-22: Rs 9.0; 2025-08-06: Rs 9.0; 2025-04-23: Rs 9.0; 2025-02-06: Rs 9.0</t>
+          <t>2026-07-29: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-23: Rs 9.0 [Q1 2026 Interim]; 2025-10-22: Rs 9.0; 2025-08-06: Rs 9.0; 2025-04-23: Rs 9.0; 2025-02-06: Rs 9.0</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>2026-04-17: Rs 6.0 [Q1 2026 Interim]; 2026-02-18: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
+          <t>2026-07-23: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-17: Rs 6.0 [Q1 2026 Interim]; 2026-02-18: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
         </is>
       </c>
     </row>
@@ -729,12 +729,12 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>2026-04-23: Rs 3.0 [Q1 2026 Interim]; 2026-02-16: Rs 3.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 2.5; 2025-07-31: Rs 2.5; 2025-04-17: Rs 2.5; 2025-01-30: Rs 2.5</t>
+          <t>2026-07-30: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-07-21: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-23: Rs 3.0 [Q1 2026 Interim]; 2026-02-16: Rs 3.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 2.5; 2025-07-31: Rs 2.5; 2025-04-17: Rs 2.5; 2025-01-30: Rs 2.5</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G11" s="9">
         <f>IF(F11=0,"-",D11*F11)</f>
@@ -921,12 +921,12 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>2026-04-15: Rs 16.0 [Q1 2026 Interim]; 2026-02-25: Rs 16.0 [FY2025 Final (excluded — not 2026)]; 2025-10-15: Rs 16.0; 2025-07-11: Rs 16.0; 2025-04-16: Rs 11.0; 2025-02-19: Rs 11.0</t>
+          <t>2026-07-22: Rs 16.0 [Q2 2026 Interim]; 2026-04-15: Rs 16.0 [Q1 2026 Interim]; 2026-02-25: Rs 16.0 [FY2025 Final (excluded — not 2026)]; 2025-10-15: Rs 16.0; 2025-07-11: Rs 16.0; 2025-04-16: Rs 11.0; 2025-02-19: Rs 11.0</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>2025-08-11: Rs 20.0</t>
+          <t>2026-07-31: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2025-08-11: Rs 20.0</t>
         </is>
       </c>
     </row>
@@ -1111,8 +1111,16 @@
         <f>IF(F15=0,"-",G15-H15)</f>
         <v/>
       </c>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-31: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1153,12 +1161,12 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29: Rs 8.5 [Q1 2026 Interim]; 2026-01-29: Rs 8.5 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
+          <t>2026-07-29: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-07-22: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-29: Rs 8.5 [Q1 2026 Interim]; 2026-01-29: Rs 8.5 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
         </is>
       </c>
     </row>
@@ -1993,12 +2001,12 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>2026-04-27: Rs 2.0 [Q1 2026 Interim]; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
+          <t>2026-07-31: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-07-22: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-27: Rs 2.0 [Q1 2026 Interim]; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2217,12 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>2026-04-30: Rs 56.0 [FY2026 Final]; 2025-10-30: Rs 46.0</t>
+          <t>2026-07-30: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-07-23: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-30: Rs 56.0 [FY2026 Final]; 2025-10-30: Rs 46.0</t>
         </is>
       </c>
     </row>
@@ -2257,12 +2265,12 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>2025-09-29: Rs 5.0; 2025-02-28: Rs 5.0</t>
+          <t>2026-07-29: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2025-09-29: Rs 5.0; 2025-02-28: Rs 5.0</t>
         </is>
       </c>
     </row>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -495,7 +495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-07-22T15:24:46. Source: PSX company payout announcements (board-meeting/announcement date).</t>
+          <t>Last updated 2026-08-03T17:20:36. Source: PSX company payout announcements (board-meeting/announcement date).</t>
         </is>
       </c>
     </row>
@@ -607,11 +607,11 @@
         <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>48</v>
@@ -931,11 +931,11 @@
         <v>0</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>6</v>
+        <v>7.75</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -987,11 +987,11 @@
         <v>0</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>17</v>
+        <v>31.5</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1842,12 +1842,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>July 22, 2026 3:47 PM</t>
+          <t>July 30, 2026 3:53 PM</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -1857,43 +1857,43 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>160%(ii) (D)</t>
+          <t>30%(ii) (D)</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>AVN</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>April 30, 2026 2:53 PM</t>
+          <t>July 30, 2026 3:50 PM</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>30/06/2026(HYR)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>10%(F) (D)</t>
+          <t>17.5%(ii) (D)</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="G3" s="7" t="inlineStr"/>
     </row>
@@ -1905,152 +1905,152 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2026 2:58 PM</t>
+          <t>July 29, 2026 3:23 PM</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>30/06/2026(HYR)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>85%(i) (D)</t>
+          <t>145%(ii) (D)</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="G4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2026 3:18 PM</t>
+          <t>July 22, 2026 3:47 PM</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>30/06/2026(HYR)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>20%(iii) (D)</t>
+          <t>160%(ii) (D)</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>AVN</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2026 3:56 PM</t>
+          <t>April 30, 2026 2:53 PM</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IIIQ)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>32.50%(iii) (D)</t>
+          <t>10%(F) (D)</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
       <c r="G6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2026 4:03 PM</t>
+          <t>April 29, 2026 2:58 PM</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IIIQ)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>15%(i) (D)</t>
+          <t>85%(i) (D)</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="G7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2026 4:02 PM</t>
+          <t>April 29, 2026 3:18 PM</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IIIQ)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>15%(i) (D)</t>
+          <t>20%(iii) (D)</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>April 27, 2026 3:50 PM</t>
+          <t>April 29, 2026 3:56 PM</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2060,26 +2060,26 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>510%(iii) (D)</t>
+          <t>32.50%(iii) (D)</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>51</v>
+        <v>3.25</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>51</v>
+        <v>3.25</v>
       </c>
       <c r="G9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>OLPL</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>April 27, 2026 3:57 PM</t>
+          <t>April 28, 2026 4:03 PM</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2089,142 +2089,142 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>15%(i) (D)</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>April 24, 2026 4:35 PM</t>
+          <t>April 28, 2026 4:02 PM</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ) - 31/03/2026(IQ)</t>
+          <t>31/03/2026(IIIQ)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>25%(i) (D)  -  25%(i) (D)</t>
+          <t>15%(i) (D)</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="G11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 3:56 PM</t>
+          <t>April 27, 2026 3:50 PM</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>31/03/2026(IIIQ)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>90%(i) (D)</t>
+          <t>510%(iii) (D)</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>OLPL</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 3:49 PM</t>
+          <t>April 27, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>31/03/2026(IIIQ)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>30%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 4:04 PM</t>
+          <t>April 24, 2026 4:35 PM</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>31/03/2026(IQ) - 31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>25%(i) (D)  -  25%(i) (D)</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="G14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2026 3:51 PM</t>
+          <t>April 23, 2026 3:56 PM</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2234,84 +2234,84 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>75%(i) (D)</t>
+          <t>90%(i) (D)</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>April 22, 2026 12:35 PM</t>
+          <t>April 23, 2026 3:49 PM</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IIIQ)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>50%(iii) (D)</t>
+          <t>30%(i) (D)</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>April 20, 2026 3:41 PM</t>
+          <t>April 23, 2026 4:04 PM</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IIIQ)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>April 17, 2026 5:10 PM</t>
+          <t>April 23, 2026 3:51 PM</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2321,142 +2321,142 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>60%(i) (D)</t>
+          <t>75%(i) (D)</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>April 15, 2026 3:51 PM</t>
+          <t>April 22, 2026 12:35 PM</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>31/03/2026(IQ)</t>
+          <t>31/03/2026(IIIQ)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>160%(i) (D)</t>
+          <t>50%(iii) (D)</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>HINOON</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>April 7, 2026 4:00 PM</t>
+          <t>April 20, 2026 3:41 PM</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/03/2026(IIIQ)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>500%(F) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>SYS</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>April 7, 2026 3:57 PM</t>
+          <t>April 17, 2026 5:10 PM</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>60%(i) (D)</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>March 26, 2026 3:54 PM</t>
+          <t>April 15, 2026 3:51 PM</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/03/2026(IQ)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>120%(F) (D)</t>
+          <t>160%(i) (D)</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>AGP</t>
+          <t>HINOON</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>March 24, 2026 4:16 PM</t>
+          <t>April 7, 2026 4:00 PM</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2466,26 +2466,26 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>60%(F) (D)</t>
+          <t>500%(F) (D)</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="G23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>ABOT</t>
+          <t>SYS</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>March 16, 2026 2:30 PM</t>
+          <t>April 7, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2495,26 +2495,26 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>400%(F) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>March 9, 2026 2:14 PM</t>
+          <t>March 26, 2026 3:54 PM</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2524,26 +2524,26 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>120%(F) (D)</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="G25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>AGP</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>February 25, 2026 12:28 PM</t>
+          <t>March 24, 2026 4:16 PM</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2553,113 +2553,113 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>160%(F) (D)</t>
+          <t>60%(F) (D)</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>ABOT</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>February 24, 2026 2:17 PM</t>
+          <t>March 16, 2026 2:30 PM</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>275%(i) (D)</t>
+          <t>400%(F) (D)</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>27.5</v>
+        <v>40</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>27.5</v>
+        <v>40</v>
       </c>
       <c r="G27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>February 24, 2026 2:38 PM</t>
+          <t>March 9, 2026 2:14 PM</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>50%(ii) (D)</t>
+          <t>25%(F) (D)</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>February 23, 2026 1:25 PM</t>
+          <t>February 25, 2026 12:28 PM</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>42.50%(ii) (D)</t>
+          <t>160%(F) (D)</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>4.25</v>
+        <v>16</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>4.25</v>
+        <v>16</v>
       </c>
       <c r="G29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>February 23, 2026 1:14 PM</t>
+          <t>February 24, 2026 2:17 PM</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2669,55 +2669,55 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>460%(ii) (D)</t>
+          <t>275%(i) (D)</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>46</v>
+        <v>27.5</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>46</v>
+        <v>27.5</v>
       </c>
       <c r="G30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>February 18, 2026 3:51 PM</t>
+          <t>February 24, 2026 2:38 PM</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>60%(F) (D)</t>
+          <t>50%(ii) (D)</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>CHCC</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>February 18, 2026 3:39 PM</t>
+          <t>February 23, 2026 1:25 PM</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -2727,55 +2727,55 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>15%(i) (D)</t>
+          <t>42.50%(ii) (D)</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1.5</v>
+        <v>4.25</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>1.5</v>
+        <v>4.25</v>
       </c>
       <c r="G32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>February 16, 2026 4:25 PM</t>
+          <t>February 23, 2026 1:14 PM</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>30%(F) (D)</t>
+          <t>460%(ii) (D)</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="G33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>February 13, 2026 3:57 PM</t>
+          <t>February 18, 2026 3:51 PM</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2785,26 +2785,26 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>45%F) (D)</t>
+          <t>60%(F) (D)</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>CHCC</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>February 13, 2026 4:00 PM</t>
+          <t>February 18, 2026 3:39 PM</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2814,26 +2814,26 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>20%(F) (D)</t>
+          <t>15%(i) (D)</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>February 12, 2026 3:27 PM</t>
+          <t>February 16, 2026 4:25 PM</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2843,26 +2843,26 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>30%(F) (D)</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>February 11, 2026 3:57 PM</t>
+          <t>February 13, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2872,55 +2872,55 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>45%(F) (D)</t>
+          <t>45%F) (D)</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="G37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>February 9, 2026 3:36 PM</t>
+          <t>February 13, 2026 4:00 PM</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(YR)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>70%(F) (D)</t>
+          <t>20%(F) (D)</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>January 29, 2026 3:14 PM</t>
+          <t>February 12, 2026 3:27 PM</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2930,118 +2930,118 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>85%(F) (D)</t>
+          <t>40%(F) (D)</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="G39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>January 27, 2026 4:55 PM</t>
+          <t>February 11, 2026 3:57 PM</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>45%(F) (D)</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="G40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>MARI</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>January 26, 2026 4:05 PM</t>
+          <t>February 9, 2026 3:36 PM</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>31/12/2025(HYR)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>83%(i) (D)</t>
+          <t>70%(F) (D)</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="G41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>October 30, 2025 4:28 PM</t>
+          <t>January 29, 2026 3:14 PM</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IQ)</t>
+          <t>31/12/2025(YR)</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>50%(i) (D)</t>
+          <t>85%(F) (D)</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>October 29, 2025 3:14 PM</t>
+          <t>January 27, 2026 4:55 PM</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IQ)</t>
+          <t>30/09/2025(HYR)</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3060,41 +3060,41 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>MARI</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>October 29, 2025 4:08 PM</t>
+          <t>January 26, 2026 4:05 PM</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IQ)</t>
+          <t>31/12/2025(HYR)</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>83%(i) (D)</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>3.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>3.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>October 28, 2025 4:40 PM</t>
+          <t>October 30, 2025 4:28 PM</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -3104,113 +3104,113 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>510%(i) (D)</t>
+          <t>50%(i) (D)</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>October 27, 2025 11:09 AM</t>
+          <t>October 29, 2025 3:14 PM</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>30/09/2025(IQ)</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>70%(iii) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>October 27, 2025 11:03 AM</t>
+          <t>October 29, 2025 4:08 PM</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>30/09/2025(IQ)</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>25%(iii) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:48 PM</t>
+          <t>October 28, 2025 4:40 PM</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>30/09/2025(IIIQ)</t>
+          <t>30/09/2025(IQ)</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>50%(iii) (D)</t>
+          <t>510%(i) (D)</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:27 PM</t>
+          <t>October 27, 2025 11:09 AM</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -3220,26 +3220,26 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>25%(iii) (D)</t>
+          <t>70%(iii) (D)</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="G49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:50 PM</t>
+          <t>October 27, 2025 11:03 AM</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3249,26 +3249,26 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>35%(iii) (D)</t>
+          <t>25%(iii) (D)</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>October 23, 2025 3:41 PM</t>
+          <t>October 23, 2025 3:48 PM</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3278,26 +3278,26 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>95%(iii) (D)</t>
+          <t>50%(iii) (D)</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="G51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>October 22, 2025 3:42 PM</t>
+          <t>October 23, 2025 3:27 PM</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3307,26 +3307,26 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>90%(iii) (D)</t>
+          <t>25%(iii) (D)</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="G52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>October 15, 2025 3:53 PM</t>
+          <t>October 23, 2025 3:50 PM</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3336,26 +3336,26 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>160%(iii) (D)</t>
+          <t>35%(iii) (D)</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>16</v>
+        <v>3.5</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>16</v>
+        <v>3.5</v>
       </c>
       <c r="G53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>October 15, 2025 3:50 PM</t>
+          <t>October 23, 2025 3:41 PM</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -3365,113 +3365,113 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>45%(iii) (D)</t>
+          <t>95%(iii) (D)</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="G54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>CPHL</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>October 2, 2025 4:35 PM</t>
+          <t>October 22, 2025 3:42 PM</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>35%(F) (D)</t>
+          <t>90%(iii) (D)</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="G55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>NML</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>September 30, 2025 3:34 PM</t>
+          <t>October 15, 2025 3:53 PM</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>20%(F) (D)</t>
+          <t>160%(iii) (D)</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>OLPL</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>September 25, 2025 4:24 PM</t>
+          <t>October 15, 2025 3:50 PM</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/09/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>35%(F) (D)</t>
+          <t>45%(iii) (D)</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>CPHL</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>September 23, 2025 4:03 PM</t>
+          <t>October 2, 2025 4:35 PM</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -3481,26 +3481,26 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>50%(F) (D)</t>
+          <t>35%(F) (D)</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>FEROZ</t>
+          <t>NML</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>September 23, 2025 4:40 PM</t>
+          <t>September 30, 2025 3:34 PM</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -3510,26 +3510,26 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>20%(F) (D)</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>OLPL</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>September 19, 2025 4:11 PM</t>
+          <t>September 25, 2025 4:24 PM</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -3539,26 +3539,26 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>35%(F) (D)</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>September 3, 2025 3:56 PM</t>
+          <t>September 23, 2025 4:03 PM</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -3568,26 +3568,26 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>50%(F) (D)</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>FEROZ</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>August 29, 2025 5:08 PM</t>
+          <t>September 23, 2025 4:40 PM</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -3597,26 +3597,26 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>500%(F) (D)</t>
+          <t>40%(F) (D)</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="G62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>DGKC</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>August 28, 2025 4:47 PM</t>
+          <t>September 19, 2025 4:11 PM</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3626,26 +3626,26 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>20%(F) (D)</t>
+          <t>25%(F) (D)</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>AGIL</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>August 28, 2025 4:44 PM</t>
+          <t>September 3, 2025 3:56 PM</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -3655,113 +3655,113 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>35%(F) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="G64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>August 27, 2025 4:33 PM</t>
+          <t>August 29, 2025 5:08 PM</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>35%(ii) (D)</t>
+          <t>500%(F) (D)</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>3.5</v>
+        <v>50</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>3.5</v>
+        <v>50</v>
       </c>
       <c r="G65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>DGKC</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>August 27, 2025 4:34 PM</t>
+          <t>August 28, 2025 4:47 PM</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>20%(F) (D)</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="G66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>AGP</t>
+          <t>AGIL</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>August 27, 2025 3:59 PM</t>
+          <t>August 28, 2025 4:44 PM</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>35%(F) (D)</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>August 26, 2025 3:34 PM</t>
+          <t>August 27, 2025 4:33 PM</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -3771,152 +3771,152 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>50%(i) (D)</t>
+          <t>35%(ii) (D)</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="G68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>CHCC</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>August 21, 2025 3:53 PM</t>
+          <t>August 27, 2025 4:34 PM</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>AGP</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>August 20, 2025 3:40 PM</t>
+          <t>August 27, 2025 3:59 PM</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>PSO</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>August 19, 2025 4:17 PM</t>
+          <t>August 26, 2025 3:34 PM</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>50%(i) (D)</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>CHCC</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>August 13, 2025 3:40 PM</t>
+          <t>August 21, 2025 3:53 PM</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>70%(ii) (D)</t>
+          <t>40%(F) (D)</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>August 13, 2025 3:38 PM</t>
+          <t>August 20, 2025 3:40 PM</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>25%(ii) (D)</t>
+          <t>25%(F) (D)</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
@@ -3930,12 +3930,12 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>LUCK</t>
+          <t>PSO</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 11:11 AM</t>
+          <t>August 19, 2025 4:17 PM</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -3945,84 +3945,84 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>200%(F) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>FCCL</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 11:05 AM</t>
+          <t>August 13, 2025 3:40 PM</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>12.50%(F) (D)</t>
+          <t>70%(ii) (D)</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1.25</v>
+        <v>7</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>1.25</v>
+        <v>7</v>
       </c>
       <c r="G75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 3:29 PM</t>
+          <t>August 13, 2025 3:38 PM</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(YR)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>500%(F) (D)</t>
+          <t>25%(ii) (D)</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>50</v>
+        <v>2.5</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>50</v>
+        <v>2.5</v>
       </c>
       <c r="G76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>MARI</t>
+          <t>LUCK</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>August 11, 2025 10:57 AM</t>
+          <t>August 11, 2025 11:11 AM</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -4032,113 +4032,113 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>217%(F) (D)</t>
+          <t>200%(F) (D)</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>21.7</v>
+        <v>20</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>21.7</v>
+        <v>20</v>
       </c>
       <c r="G77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>FCCL</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>August 6, 2025 3:49 PM</t>
+          <t>August 11, 2025 11:05 AM</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>90%(ii) (D)</t>
+          <t>12.50%(F) (D)</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>9</v>
+        <v>1.25</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>9</v>
+        <v>1.25</v>
       </c>
       <c r="G78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>July 31, 2025 3:49 PM</t>
+          <t>August 11, 2025 3:29 PM</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>45%(ii) (D)</t>
+          <t>500%(F) (D)</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>4.5</v>
+        <v>50</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>4.5</v>
+        <v>50</v>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>MARI</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>July 31, 2025 3:53 PM</t>
+          <t>August 11, 2025 10:57 AM</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>30/06/2025(HYR)</t>
+          <t>30/06/2025(YR)</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>25%(ii) (D)</t>
+          <t>217%(F) (D)</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>2.5</v>
+        <v>21.7</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>2.5</v>
+        <v>21.7</v>
       </c>
       <c r="G80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>July 30, 2025 3:24 PM</t>
+          <t>August 6, 2025 3:49 PM</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -4148,26 +4148,26 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>42.50%(ii) (D)</t>
+          <t>90%(ii) (D)</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>4.25</v>
+        <v>9</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>4.25</v>
+        <v>9</v>
       </c>
       <c r="G81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>July 29, 2025 3:26 PM</t>
+          <t>July 31, 2025 3:49 PM</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -4177,26 +4177,26 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>120%(ii) (D)</t>
+          <t>45%(ii) (D)</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="G82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>July 11, 2025 5:05 PM</t>
+          <t>July 31, 2025 3:53 PM</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -4206,113 +4206,113 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>160%(II) (D)</t>
+          <t>25%(ii) (D)</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="G83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>April 30, 2025 4:16 PM</t>
+          <t>July 30, 2025 3:24 PM</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>30%(iii) (D)</t>
+          <t>42.50%(ii) (D)</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="G84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>April 29, 2025 2:46 PM</t>
+          <t>July 29, 2025 3:26 PM</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>10%(iii) (D)</t>
+          <t>120%(ii) (D)</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2025 3:39 PM</t>
+          <t>July 11, 2025 5:05 PM</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>30/06/2025(HYR)</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>70%(i) (D)</t>
+          <t>160%(II) (D)</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>April 28, 2025 12:00 PM</t>
+          <t>April 30, 2025 4:16 PM</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -4322,84 +4322,84 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>500%(iii) (D)</t>
+          <t>30%(iii) (D)</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>April 25, 2025 4:31 PM</t>
+          <t>April 29, 2025 2:46 PM</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>45%(i) (D)</t>
+          <t>10%(iii) (D)</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="G88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>FFC</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>April 25, 2025 5:30 PM</t>
+          <t>April 28, 2025 3:39 PM</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IIIQ)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>20%(iii) (D)</t>
+          <t>70%(i) (D)</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>April 25, 2025 5:26 PM</t>
+          <t>April 28, 2025 12:00 PM</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -4409,26 +4409,26 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>20%(iii) (D)</t>
+          <t>500%(iii) (D)</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>April 24, 2025 4:02 PM</t>
+          <t>April 25, 2025 4:31 PM</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -4438,26 +4438,26 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>35%(i) (D)</t>
+          <t>45%(i) (D)</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>OLPL</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>April 24, 2025 12:45 PM</t>
+          <t>April 25, 2025 5:30 PM</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>20%(iii) (D)</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -4481,41 +4481,41 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2025 3:39 PM</t>
+          <t>April 25, 2025 5:26 PM</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>90%(i) (D)</t>
+          <t>20%(iii) (D)</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G93" s="7" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>BAHL</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>April 23, 2025 3:22 PM</t>
+          <t>April 24, 2025 4:02 PM</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -4525,55 +4525,55 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>25%(i) (D)</t>
+          <t>35%(i) (D)</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>OLPL</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>April 22, 2025 5:01 PM</t>
+          <t>April 24, 2025 12:45 PM</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>31/03/2025(IQ)</t>
+          <t>31/03/2025(IIIQ)</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>22.5%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="G95" s="7" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>April 21, 2025 4:10 PM</t>
+          <t>April 23, 2025 3:39 PM</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -4583,26 +4583,26 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>70%(i) (D)</t>
+          <t>90%(i) (D)</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G96" s="7" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>April 17, 2025 3:56 PM</t>
+          <t>April 23, 2025 3:22 PM</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -4626,12 +4626,12 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>April 16, 2025 4:52 PM</t>
+          <t>April 22, 2025 5:01 PM</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -4641,113 +4641,113 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>110%(i) (D)</t>
+          <t>22.5%(i) (D)</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>11</v>
+        <v>2.25</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>11</v>
+        <v>2.25</v>
       </c>
       <c r="G98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>HINOON</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>March 26, 2025 2:45 PM</t>
+          <t>April 21, 2025 4:10 PM</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>400%(F) (D)</t>
+          <t>70%(i) (D)</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G99" s="7" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>March 24, 2025 2:13 PM</t>
+          <t>April 17, 2025 3:56 PM</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>25%(i) (D)</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="G100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>SYS</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>March 24, 2025 2:14 PM</t>
+          <t>April 16, 2025 4:52 PM</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/03/2025(IQ)</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>60%(F) (D)</t>
+          <t>110%(i) (D)</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G101" s="7" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>HINOON</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>March 14, 2025 1:12 PM</t>
+          <t>March 26, 2025 2:45 PM</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -4757,142 +4757,142 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>42.5%(F) (D)</t>
+          <t>400%(F) (D)</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>4.25</v>
+        <v>40</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>4.25</v>
+        <v>40</v>
       </c>
       <c r="G102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 4:26 PM</t>
+          <t>March 24, 2025 2:13 PM</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/12/2024(YR)</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>20%(ii) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>OGDC</t>
+          <t>SYS</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 4:32 PM</t>
+          <t>March 24, 2025 2:14 PM</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/12/2024(YR)</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>40.50% (D)</t>
+          <t>60%(F) (D)</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>INDU</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 10:58 AM</t>
+          <t>March 14, 2025 1:12 PM</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/12/2024(YR)</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>370%(ii) (D)</t>
+          <t>42.5%(F) (D)</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>37</v>
+        <v>4.25</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>37</v>
+        <v>4.25</v>
       </c>
       <c r="G105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>AGP</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>February 28, 2025 11:04 AM</t>
+          <t>February 28, 2025 4:26 PM</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/12/2024(HYR)</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>40%(F) (D)</t>
+          <t>20%(ii) (D)</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>February 27, 2025 2:56 PM</t>
+          <t>February 28, 2025 4:32 PM</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
@@ -4902,26 +4902,26 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>20%(i) (D)</t>
+          <t>40.50% (D)</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>INDU</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>February 26, 2025 12:53 PM</t>
+          <t>February 28, 2025 10:58 AM</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -4931,171 +4931,171 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>50%(i) (D)</t>
+          <t>370%(ii) (D)</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="G108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>CHCC</t>
+          <t>AGP</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>February 21, 2025 2:43 PM</t>
+          <t>February 28, 2025 11:04 AM</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/12/2024(YR)</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>15%(i) (D)</t>
+          <t>40%(F) (D)</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G109" s="7" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>ALTN</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>February 21, 2025 5:00 PM</t>
+          <t>February 27, 2025 2:56 PM</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31/12/2024(HYR)</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>97%(i) (D)</t>
+          <t>20%(i) (D)</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>2</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>2</v>
       </c>
       <c r="G110" s="7" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>February 20, 2025 3:24 PM</t>
+          <t>February 26, 2025 12:53 PM</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/12/2024(HYR)</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>45%(F) (D)</t>
+          <t>50%(i) (D)</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>ABOT</t>
+          <t>CHCC</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>February 20, 2025 3:45 PM</t>
+          <t>February 21, 2025 2:43 PM</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>31/12/2024(HYR)</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>100%(F) (D)</t>
+          <t>15%(i) (D)</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="G112" s="7" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>ALTN</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>February 19, 2025 3:45 PM</t>
+          <t>February 21, 2025 5:00 PM</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(YR)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>42.5%(F) (D)</t>
+          <t>97%(i) (D)</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>4.25</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>4.25</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G113" s="7" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>February 19, 2025 3:42 PM</t>
+          <t>February 20, 2025 3:24 PM</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -5105,26 +5105,26 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>110%(F) (D)</t>
+          <t>45%(F) (D)</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="G114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>MEBL</t>
+          <t>ABOT</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>February 13, 2025 3:30 PM</t>
+          <t>February 20, 2025 3:45 PM</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -5134,26 +5134,26 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>70%(F) (D)</t>
+          <t>100%(F) (D)</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>EFERT</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>February 10, 2025 3:39 PM</t>
+          <t>February 19, 2025 3:45 PM</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -5163,26 +5163,26 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>80%(F) (D)</t>
+          <t>42.5%(F) (D)</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>8</v>
+        <v>4.25</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>8</v>
+        <v>4.25</v>
       </c>
       <c r="G116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>February 6, 2025 4:25 PM</t>
+          <t>February 19, 2025 3:42 PM</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
@@ -5192,26 +5192,26 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>90%(F) (D)</t>
+          <t>110%(F) (D)</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G117" s="7" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>BAFL</t>
+          <t>MEBL</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>January 30, 2025 4:00 PM</t>
+          <t>February 13, 2025 3:30 PM</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -5221,26 +5221,26 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>25%(F) (D)</t>
+          <t>70%(F) (D)</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="G118" s="7" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>BAHL</t>
+          <t>EFERT</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>January 30, 2025 4:05 PM</t>
+          <t>February 10, 2025 3:39 PM</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
@@ -5250,26 +5250,26 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>65%(F) (D)</t>
+          <t>80%(F) (D)</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="G119" s="7" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>FFC</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>January 29, 2025 3:36 PM</t>
+          <t>February 6, 2025 4:25 PM</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -5279,74 +5279,161 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>210%(F) (D)</t>
+          <t>90%(F) (D)</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G120" s="7" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>BAFL</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>January 27, 2025 4:28 PM</t>
+          <t>January 30, 2025 4:00 PM</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>31/12/2024(HYR)</t>
+          <t>31/12/2024(YR)</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>250%(i) (D)</t>
+          <t>25%(F) (D)</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="G121" s="7" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
+          <t>BAHL</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>January 30, 2025 4:05 PM</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>65%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>FFC</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>January 29, 2025 3:36 PM</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(YR)</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>210%(F) (D)</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>January 27, 2025 4:28 PM</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2024(HYR)</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>250%(i) (D)</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
           <t>NCPL</t>
         </is>
       </c>
-      <c r="B122" s="5" t="inlineStr">
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>November 13, 2024 4:33 PM</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>50%(I) (D)</t>
         </is>
       </c>
-      <c r="E122" s="5" t="n">
+      <c r="E125" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F122" s="5" t="n">
+      <c r="F125" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G122" s="7" t="inlineStr"/>
+      <c r="G125" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-08-05T08:36:23. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+          <t>Last updated 2026-08-05T08:44:10. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>2026-07-23: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-17: Rs 6.0 [Q1 2026 Interim]; 2026-02-18: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
+          <t>2026-08-04: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-07-23: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-17: Rs 6.0 [Q1 2026 Interim]; 2026-02-18: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G7" s="9">
         <f>IF(F7=0,"-",D7*F7)</f>
@@ -734,7 +734,7 @@
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-07-21: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-23: Rs 3.0 [Q1 2026 Interim]; 2026-02-16: Rs 3.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 2.5; 2025-07-31: Rs 2.5; 2025-04-17: Rs 2.5; 2025-01-30: Rs 2.5</t>
+          <t>2026-07-30: Rs 3.0 [FY2026 Final]; 2026-07-21: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-23: Rs 3.0 [Q1 2026 Interim]; 2026-02-16: Rs 3.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 2.5; 2025-07-31: Rs 2.5; 2025-04-17: Rs 2.5; 2025-01-30: Rs 2.5</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>8.5</v>
+        <v>23</v>
       </c>
       <c r="G16" s="9">
         <f>IF(F16=0,"-",D16*F16)</f>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>2026-07-29: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-07-22: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-29: Rs 8.5 [Q1 2026 Interim]; 2026-01-29: Rs 8.5 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
+          <t>2026-07-29: Rs 14.5 [FY2026 Final]; 2026-07-22: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-29: Rs 8.5 [Q1 2026 Interim]; 2026-01-29: Rs 8.5 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 9.5; 2025-07-29: Rs 12.0; 2025-04-28: Rs 7.0; 2025-01-29: Rs 21.0</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G34" s="9">
         <f>IF(F34=0,"-",D34*F34)</f>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-07-22: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-27: Rs 2.0 [Q1 2026 Interim]; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
+          <t>2026-07-31: Rs 2.0 [FY2026 Final]; 2026-07-22: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-27: Rs 2.0 [Q1 2026 Interim]; 2026-02-09: Rs 0.0; 2025-10-29: Rs 0.0; 2025-08-21: Rs 2.0; 2025-02-24: Rs 3.0</t>
         </is>
       </c>
     </row>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-08-05T08:44:10. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+          <t>Last updated 2026-08-05T16:15:59. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>2026-08-04: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-07-23: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-17: Rs 6.0 [Q1 2026 Interim]; 2026-02-18: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
+          <t>2026-08-04: Rs 0.0; 2026-07-23: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-17: Rs 6.0 [Q1 2026 Interim]; 2026-02-18: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-10-23: Rs 5.0; 2025-07-31: Rs 4.5; 2025-04-25: Rs 4.5; 2025-02-19: Rs 4.25</t>
         </is>
       </c>
     </row>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-08-05T16:15:59. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+          <t>Last updated 2026-08-07T10:18:07. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
         </is>
       </c>
     </row>
@@ -614,10 +614,10 @@
         <v>362505</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G5" s="9">
         <f>IF(F5=0,"-",D5*F5)</f>
@@ -633,12 +633,12 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>2026-07-29: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-23: Rs 9.0 [Q1 2026 Interim]; 2025-10-22: Rs 9.0; 2025-08-06: Rs 9.0; 2025-04-23: Rs 9.0; 2025-02-06: Rs 9.0</t>
+          <t>2026-08-06: Rs 9.0 [FY2026 Final]; 2026-07-29: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-23: Rs 9.0 [Q1 2026 Interim]; 2025-10-22: Rs 9.0; 2025-08-06: Rs 9.0; 2025-04-23: Rs 9.0; 2025-02-06: Rs 9.0</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-23: Rs 7.5 [Q1 2026 Interim]; 2026-02-09: Rs 7.0 [FY2025 Final (excluded — not 2026)]; 2025-10-27: Rs 7.0; 2025-08-13: Rs 7.0; 2025-04-21: Rs 7.0; 2025-02-13: Rs 7.0</t>
+          <t>2026-08-06: Rs 0.0; 2026-04-23: Rs 7.5 [Q1 2026 Interim]; 2026-02-09: Rs 7.0 [FY2025 Final (excluded — not 2026)]; 2025-10-27: Rs 7.0; 2025-08-13: Rs 7.0; 2025-04-21: Rs 7.0; 2025-02-13: Rs 7.0</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>2026-02-19: Rs 1.0 [FY2025 Final (excluded — not 2026)]; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
+          <t>2026-08-06: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-02-19: Rs 1.0 [FY2025 Final (excluded — not 2026)]; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
         </is>
       </c>
     </row>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-08-07T10:18:07. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+          <t>Last updated 2026-08-10T10:41:43. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2025-08-11: Rs 20.0</t>
+          <t>2026-08-10: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-07-31: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2025-08-11: Rs 20.0</t>
         </is>
       </c>
     </row>
@@ -1447,8 +1447,16 @@
         <f>IF(F22=0,"-",G22-H22)</f>
         <v/>
       </c>
-      <c r="J22" s="7" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-10: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-08-10T10:41:43. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+          <t>Last updated 2026-08-11T10:17:34. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
         </is>
       </c>
     </row>
@@ -950,10 +950,10 @@
         <v>24000</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G12" s="9">
         <f>IF(F12=0,"-",D12*F12)</f>
@@ -974,7 +974,7 @@
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>2026-08-10: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-07-31: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2025-08-11: Rs 20.0</t>
+          <t>2026-08-10: Rs 25.0 [FY2026 Final]; 2026-07-31: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2025-08-11: Rs 20.0</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>2025-08-11: Rs 1.25</t>
+          <t>2026-08-11: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2025-08-11: Rs 1.25</t>
         </is>
       </c>
     </row>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-08-11T10:17:34. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+          <t>Last updated 2026-08-12T10:33:26. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
         </is>
       </c>
     </row>
@@ -1046,10 +1046,10 @@
         <v>436625</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G14" s="9">
         <f>IF(F14=0,"-",D14*F14)</f>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2025-08-11: Rs 1.25</t>
+          <t>2026-08-11: Rs 1.5 [FY2026 Final]; 2025-08-11: Rs 1.25</t>
         </is>
       </c>
     </row>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-08-12T10:33:26. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+          <t>Last updated 2026-08-13T10:35:59. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>2026-04-24: Rs 5.0 [Q1 2026 Interim]; 2026-02-13: Rs 0.0; 2025-10-27: Rs 2.5; 2025-08-13: Rs 2.5; 2025-04-23: Rs 2.5; 2025-02-20: Rs 4.5</t>
+          <t>2026-08-13: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-24: Rs 5.0 [Q1 2026 Interim]; 2026-02-13: Rs 0.0; 2025-10-27: Rs 2.5; 2025-08-13: Rs 2.5; 2025-04-23: Rs 2.5; 2025-02-20: Rs 4.5</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-08-27: Rs 2.0; 2025-02-28: Rs 4.0</t>
+          <t>2026-08-13: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-03-24: Rs 6.0 [FY2025 Final (excluded — not 2026)]; 2025-08-27: Rs 2.0; 2025-02-28: Rs 4.0</t>
         </is>
       </c>
     </row>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-08-13T10:35:59. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+          <t>Last updated 2026-08-14T10:31:04. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
         </is>
       </c>
     </row>
@@ -854,10 +854,10 @@
         <v>625687</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="G10" s="9">
         <f>IF(F10=0,"-",D10*F10)</f>
@@ -878,7 +878,7 @@
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>2026-08-13: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-04-24: Rs 5.0 [Q1 2026 Interim]; 2026-02-13: Rs 0.0; 2025-10-27: Rs 2.5; 2025-08-13: Rs 2.5; 2025-04-23: Rs 2.5; 2025-02-20: Rs 4.5</t>
+          <t>2026-08-13: Rs 2.5 [FY2026 Final]; 2026-04-24: Rs 5.0 [Q1 2026 Interim]; 2026-02-13: Rs 0.0; 2025-10-27: Rs 2.5; 2025-08-13: Rs 2.5; 2025-04-23: Rs 2.5; 2025-02-20: Rs 4.5</t>
         </is>
       </c>
     </row>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-08-14T10:31:04. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+          <t>Last updated 2026-08-18T09:55:33. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>2026-08-06: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-02-19: Rs 1.0 [FY2025 Final (excluded — not 2026)]; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
+          <t>2026-08-18: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-08-06: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-02-19: Rs 1.0 [FY2025 Final (excluded — not 2026)]; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
         </is>
       </c>
     </row>

--- a/PSX_Dividend_Tracker.xlsx
+++ b/PSX_Dividend_Tracker.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last updated 2026-08-18T09:55:33. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
+          <t>Last updated 2026-08-19T09:56:24. Source: PSX company payout announcements (board-meeting/announcement date). Quantity sourced from Cash Dividend 1 (1).xlsx. Gross/Tax/Net Cash Dividend are Quantity x Dividend YTD 2026 (see formulas in G:I; tax rate in B3).</t>
         </is>
       </c>
     </row>
@@ -1806,10 +1806,10 @@
         <v>23655</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G30" s="9">
         <f>IF(F30=0,"-",D30*F30)</f>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>2026-08-18: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-08-06: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-02-19: Rs 1.0 [FY2025 Final (excluded — not 2026)]; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
+          <t>2026-08-18: Rs 3.0 [FY2026 Final]; 2026-08-06: unconfirmed [scanned PDF (no extractable text) found via announcement tabs — could not confirm a dividend amount automatically]; 2026-02-19: Rs 1.0 [FY2025 Final (excluded — not 2026)]; 2025-08-20: Rs 2.0; 2025-02-20: Rs 1.0</t>
         </is>
       </c>
     </row>
